--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-13T00:31:30+00:00</t>
+          <t>2026-09-14T00:34:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14T00:34:11+00:00</t>
+          <t>2026-09-15T01:07:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15T01:07:29+00:00</t>
+          <t>2026-09-16T00:55:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-16T00:55:35+00:00</t>
+          <t>2026-09-17T02:25:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17T02:25:08+00:00</t>
+          <t>2026-09-18T00:56:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18T00:56:30+00:00</t>
+          <t>2026-09-19T00:50:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-19T00:50:53+00:00</t>
+          <t>2026-09-20T00:33:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-20T00:33:56+00:00</t>
+          <t>2026-09-21T00:43:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21T00:43:20+00:00</t>
+          <t>2026-09-22T01:25:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22T01:25:24+00:00</t>
+          <t>2026-09-23T01:06:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-23T01:06:58+00:00</t>
+          <t>2026-09-24T01:01:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-24T01:01:59+00:00</t>
+          <t>2026-09-25T01:04:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-25T01:04:34+00:00</t>
+          <t>2026-09-26T01:06:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-26T01:06:19+00:00</t>
+          <t>2026-09-27T01:03:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-27T01:03:46+00:00</t>
+          <t>2026-09-28T01:22:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28T01:22:36+00:00</t>
+          <t>2026-09-29T02:27:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29T02:27:28+00:00</t>
+          <t>2026-09-30T01:46:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-30T01:46:39+00:00</t>
+          <t>2026-10-01T01:45:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-01T01:45:02+00:00</t>
+          <t>2026-10-02T01:55:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02T01:55:05+00:00</t>
+          <t>2026-10-03T01:38:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-03T01:38:06+00:00</t>
+          <t>2026-10-04T02:18:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-04T02:18:34+00:00</t>
+          <t>2026-10-05T01:27:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-05T01:27:07+00:00</t>
+          <t>2026-10-06T02:37:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06T02:37:53+00:00</t>
+          <t>2026-10-07T01:56:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07T01:56:11+00:00</t>
+          <t>2026-10-08T02:24:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08T02:24:16+00:00</t>
+          <t>2026-10-09T02:42:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-09T02:42:37+00:00</t>
+          <t>2026-10-10T02:02:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T02:02:07+00:00</t>
+          <t>2026-10-10T09:16:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T09:16:46+00:00</t>
+          <t>2026-10-10T16:04:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T16:04:28+00:00</t>
+          <t>2026-10-10T22:09:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T22:09:13+00:00</t>
+          <t>2026-10-11T01:27:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T01:27:04+00:00</t>
+          <t>2026-10-11T09:33:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T09:33:54+00:00</t>
+          <t>2026-10-11T16:30:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T16:30:16+00:00</t>
+          <t>2026-10-11T22:37:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T22:37:55+00:00</t>
+          <t>2026-10-12T01:57:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T01:57:34+00:00</t>
+          <t>2026-10-12T10:03:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T10:03:56+00:00</t>
+          <t>2026-10-12T20:05:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T20:05:50+00:00</t>
+          <t>2026-10-13T03:19:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T03:19:18+00:00</t>
+          <t>2026-10-13T14:44:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T14:44:23+00:00</t>
+          <t>2026-10-13T20:29:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T20:29:29+00:00</t>
+          <t>2026-10-14T01:31:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T01:31:56+00:00</t>
+          <t>2026-10-14T08:16:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T08:16:38+00:00</t>
+          <t>2026-10-14T15:40:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T15:40:44+00:00</t>
+          <t>2026-10-14T22:01:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T22:01:16+00:00</t>
+          <t>2026-10-15T01:10:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T01:10:00+00:00</t>
+          <t>2026-10-15T07:54:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T07:54:15+00:00</t>
+          <t>2026-10-15T15:27:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T15:27:07+00:00</t>
+          <t>2026-10-15T21:54:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T21:54:54+00:00</t>
+          <t>2026-10-16T00:56:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T00:56:41+00:00</t>
+          <t>2026-10-16T07:45:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T07:45:45+00:00</t>
+          <t>2026-10-16T15:06:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T15:06:46+00:00</t>
+          <t>2026-10-16T21:52:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T21:52:50+00:00</t>
+          <t>2026-10-17T00:56:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T00:56:54+00:00</t>
+          <t>2026-10-17T07:23:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T07:23:05+00:00</t>
+          <t>2026-10-17T14:03:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T14:03:11+00:00</t>
+          <t>2026-10-17T17:42:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T17:42:40+00:00</t>
+          <t>2026-10-17T21:11:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T21:11:36+00:00</t>
+          <t>2026-10-18T00:32:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T00:32:10+00:00</t>
+          <t>2026-10-18T07:37:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T07:37:12+00:00</t>
+          <t>2026-10-18T14:15:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T14:15:13+00:00</t>
+          <t>2026-10-18T17:43:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T17:43:33+00:00</t>
+          <t>2026-10-18T21:13:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T21:13:38+00:00</t>
+          <t>2026-10-19T00:39:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T00:39:11+00:00</t>
+          <t>2026-10-19T08:21:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T08:21:04+00:00</t>
+          <t>2026-10-19T17:18:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T17:18:31+00:00</t>
+          <t>2026-10-19T22:43:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T22:43:53+00:00</t>
+          <t>2026-10-20T01:24:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T01:24:04+00:00</t>
+          <t>2026-10-20T08:05:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T08:05:12+00:00</t>
+          <t>2026-10-20T15:31:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T15:31:30+00:00</t>
+          <t>2026-10-20T22:01:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://worldjusticeproject.org/rule-of-law-index/data/2025.csv</t>
+          <t>https://worldjusticeproject.org/rule-of-law-index/data/2026.csv</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T22:01:43+00:00</t>
+          <t>2026-10-21T01:10:47+00:00</t>
         </is>
       </c>
     </row>
@@ -640,31 +640,31 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.30764429</v>
+        <v>0.3051298</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.34064524</v>
+        <v>0.33619149</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.29146237</v>
+        <v>0.28523158</v>
       </c>
       <c r="H2" s="5" t="n">
-        <v>0.31460353</v>
+        <v>0.31521618</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>0.24010618</v>
+        <v>0.23056801</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>0.36720617</v>
+        <v>0.37104863</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>0.34623099</v>
+        <v>0.34716456</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>0.31598228</v>
+        <v>0.31400671</v>
       </c>
       <c r="M2" s="5" t="n">
-        <v>0.24491759</v>
+        <v>0.24161122</v>
       </c>
     </row>
     <row r="3">
@@ -689,31 +689,31 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.48877582</v>
+        <v>0.48160442</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.42778642</v>
+        <v>0.41735508</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.37614294</v>
+        <v>0.36941649</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0.47864012</v>
+        <v>0.46945902</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>0.56595418</v>
+        <v>0.56228587</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>0.77369104</v>
+        <v>0.77332176</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>0.42762436</v>
+        <v>0.4152997</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>0.45522716</v>
+        <v>0.44318509</v>
       </c>
       <c r="M3" s="5" t="n">
-        <v>0.40514035</v>
+        <v>0.40251236</v>
       </c>
     </row>
     <row r="4">
@@ -738,31 +738,31 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.48857478</v>
+        <v>0.49264188</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.47197537</v>
+        <v>0.47557645</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.45475017</v>
+        <v>0.4600544</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.35521642</v>
+        <v>0.35338258</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.42106099</v>
+        <v>0.42667489</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.75866256</v>
+        <v>0.7627363</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.48389982</v>
+        <v>0.48278716</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0.54615472</v>
+        <v>0.54649481</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.41687818</v>
+        <v>0.43342846</v>
       </c>
     </row>
     <row r="5">
@@ -787,31 +787,31 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.42317338</v>
+        <v>0.42178684</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.40376636</v>
+        <v>0.4042794</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.43315696</v>
+        <v>0.44052732</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.3872482</v>
+        <v>0.38179555</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.37470521</v>
+        <v>0.37602082</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.58301828</v>
+        <v>0.58193246</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.43203018</v>
+        <v>0.42241065</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.42901044</v>
+        <v>0.42579256</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0.34245139</v>
+        <v>0.34153599</v>
       </c>
     </row>
     <row r="6">
@@ -836,31 +836,31 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.6371966100000001</v>
+        <v>0.6364272399999999</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.61657498</v>
+        <v>0.61477601</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.62833664</v>
+        <v>0.62257688</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.5219497</v>
+        <v>0.52102505</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.70543354</v>
+        <v>0.7056457900000001</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.79094666</v>
+        <v>0.79094665</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0.61971595</v>
+        <v>0.6205065400000001</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.68488528</v>
+        <v>0.68729158</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.52973009</v>
+        <v>0.52864941</v>
       </c>
     </row>
     <row r="7">
@@ -885,31 +885,31 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.54045581</v>
+        <v>0.53853879</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.54428276</v>
+        <v>0.5367901</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.45026983</v>
+        <v>0.45085833</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.6115028</v>
+        <v>0.62258972</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.67447673</v>
+        <v>0.65984831</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.60572683</v>
+        <v>0.60206147</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.50532108</v>
+        <v>0.50771903</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.54957356</v>
+        <v>0.54784018</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.38249288</v>
+        <v>0.38060322</v>
       </c>
     </row>
     <row r="8">
@@ -934,31 +934,31 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.79630136</v>
+        <v>0.795126</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.80838137</v>
+        <v>0.80609951</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.83194943</v>
+        <v>0.82930445</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.80864674</v>
+        <v>0.80956918</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.78728942</v>
+        <v>0.78544166</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.87084541</v>
+        <v>0.86898992</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.8071711</v>
+        <v>0.8037021600000001</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.74069662</v>
+        <v>0.74472363</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.71543074</v>
+        <v>0.71317752</v>
       </c>
     </row>
     <row r="9">
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.79426923</v>
+        <v>0.79674679</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.82179855</v>
+        <v>0.81041965</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.7956231</v>
+        <v>0.79704218</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.68238727</v>
+        <v>0.70103835</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.82833905</v>
+        <v>0.8328497</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.90910148</v>
+        <v>0.90529887</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.79921966</v>
+        <v>0.79696627</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.73383814</v>
+        <v>0.73640746</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.78384657</v>
+        <v>0.7939518</v>
       </c>
     </row>
     <row r="10">
@@ -1032,31 +1032,31 @@
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.58396263</v>
+        <v>0.58523558</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.58019897</v>
+        <v>0.58327767</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.61821741</v>
+        <v>0.61588264</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.47622905</v>
+        <v>0.47848118</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.631493</v>
+        <v>0.63552031</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.72351213</v>
+        <v>0.7278980900000001</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.5088038</v>
+        <v>0.5094119499999999</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.56269315</v>
+        <v>0.56141857</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>0.57055354</v>
+        <v>0.56999418</v>
       </c>
     </row>
     <row r="11">
@@ -1081,31 +1081,31 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.3912668</v>
+        <v>0.39348581</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.37307648</v>
+        <v>0.38236675</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.33980004</v>
+        <v>0.35014812</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.40972585</v>
+        <v>0.40621674</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.30373508</v>
+        <v>0.30327355</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.63139947</v>
+        <v>0.63013991</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.39205806</v>
+        <v>0.39729731</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.36338391</v>
+        <v>0.36293591</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.3169555</v>
+        <v>0.31550823</v>
       </c>
     </row>
     <row r="12">
@@ -1130,31 +1130,31 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.66109376</v>
+        <v>0.66226691</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.65199045</v>
+        <v>0.65145415</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.70230028</v>
+        <v>0.69892249</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.55682272</v>
+        <v>0.55242245</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.74040006</v>
+        <v>0.74114503</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.80307788</v>
+        <v>0.8021475300000001</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.6378053299999999</v>
+        <v>0.64593741</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.6131571099999999</v>
+        <v>0.62114889</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.58319626</v>
+        <v>0.58495734</v>
       </c>
     </row>
     <row r="13">
@@ -1179,31 +1179,31 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.44475383</v>
+        <v>0.44460324</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.25776191</v>
+        <v>0.26015164</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.49261943</v>
+        <v>0.49816831</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.30212511</v>
+        <v>0.30276984</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.33048959</v>
+        <v>0.32758787</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.81037321</v>
+        <v>0.81018678</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.43009839</v>
+        <v>0.43133234</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0.55201025</v>
+        <v>0.5447287</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>0.38255278</v>
+        <v>0.38190046</v>
       </c>
     </row>
     <row r="14">
@@ -1228,31 +1228,31 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.78141921</v>
+        <v>0.77873389</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.80519042</v>
+        <v>0.80981445</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.79332091</v>
+        <v>0.7823026</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.7660782</v>
+        <v>0.7666903</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.84094397</v>
+        <v>0.83666428</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.82144025</v>
+        <v>0.81335041</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.79315356</v>
+        <v>0.78907631</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.73318196</v>
+        <v>0.7323066499999999</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.69804443</v>
+        <v>0.69966613</v>
       </c>
     </row>
     <row r="15">
@@ -1277,31 +1277,31 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.49650438</v>
+        <v>0.49481559</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.48430781</v>
+        <v>0.48510507</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.45268062</v>
+        <v>0.44943064</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.45324044</v>
+        <v>0.44880254</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.5257829000000001</v>
+        <v>0.52223855</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.7131675</v>
+        <v>0.71303673</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.41671861</v>
+        <v>0.42018434</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.52630446</v>
+        <v>0.52324629</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>0.39983266</v>
+        <v>0.39648054</v>
       </c>
     </row>
     <row r="16">
@@ -1326,31 +1326,31 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.47187284</v>
+        <v>0.47297701</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.49354998</v>
+        <v>0.49477459</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.40499771</v>
+        <v>0.4117988</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.37983473</v>
+        <v>0.38072608</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.50793079</v>
+        <v>0.5091748</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.68134207</v>
+        <v>0.68066706</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.46715008</v>
+        <v>0.46002403</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.4319594</v>
+        <v>0.43114829</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.40821796</v>
+        <v>0.41550242</v>
       </c>
     </row>
     <row r="17">
@@ -1375,31 +1375,31 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.3654158</v>
+        <v>0.3678347</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.34410982</v>
+        <v>0.34958468</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.23432205</v>
+        <v>0.24120252</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.44675881</v>
+        <v>0.45269765</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.43528286</v>
+        <v>0.43412391</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.60213645</v>
+        <v>0.60537175</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.36714666</v>
+        <v>0.36391288</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.3034101</v>
+        <v>0.30237887</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0.19015966</v>
+        <v>0.19340534</v>
       </c>
     </row>
     <row r="18">
@@ -1424,31 +1424,31 @@
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.51994863</v>
+        <v>0.5227826</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.46856297</v>
+        <v>0.47211965</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.43279845</v>
+        <v>0.42975723</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.48133331</v>
+        <v>0.49084486</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.58795986</v>
+        <v>0.5955613199999999</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.77370854</v>
+        <v>0.77449315</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.48435135</v>
+        <v>0.4880266</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.45859056</v>
+        <v>0.46416876</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.47228401</v>
+        <v>0.46728921</v>
       </c>
     </row>
     <row r="19">
@@ -1473,31 +1473,31 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.59548103</v>
+        <v>0.5955671</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.62114217</v>
+        <v>0.60912988</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.57822944</v>
+        <v>0.5996076</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.47988209</v>
+        <v>0.46668358</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.5874537</v>
+        <v>0.58748895</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.71681353</v>
+        <v>0.71486346</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.5895083800000001</v>
+        <v>0.59567828</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.6142197700000001</v>
+        <v>0.6102439</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>0.57659914</v>
+        <v>0.58084111</v>
       </c>
     </row>
     <row r="20">
@@ -1522,31 +1522,31 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.50271197</v>
+        <v>0.50547301</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.51671335</v>
+        <v>0.51547856</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.45254125</v>
+        <v>0.45526011</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.5851915</v>
+        <v>0.58291187</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.50457425</v>
+        <v>0.50459025</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.62229715</v>
+        <v>0.6181302</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.5002974</v>
+        <v>0.51796901</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.50753027</v>
+        <v>0.5144609999999999</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.33255056</v>
+        <v>0.33498307</v>
       </c>
     </row>
     <row r="21">
@@ -1571,31 +1571,31 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.55251684</v>
+        <v>0.54608104</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.49657126</v>
+        <v>0.48697843</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.45381988</v>
+        <v>0.44450008</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.59072596</v>
+        <v>0.5898985</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.59951054</v>
+        <v>0.5909444700000001</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.7820924500000001</v>
+        <v>0.77786054</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.5195247</v>
+        <v>0.5157239</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.5315545699999999</v>
+        <v>0.52570314</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>0.44633539</v>
+        <v>0.43703929</v>
       </c>
     </row>
     <row r="22">
@@ -1620,31 +1620,31 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.45197536</v>
+        <v>0.44633536</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.47872202</v>
+        <v>0.46596862</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.42700927</v>
+        <v>0.41979066</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.44288663</v>
+        <v>0.44139558</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.49483161</v>
+        <v>0.48465552</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.41150054</v>
+        <v>0.41282322</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.46045457</v>
+        <v>0.45629686</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.43400937</v>
+        <v>0.42468023</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>0.46638883</v>
+        <v>0.46507217</v>
       </c>
     </row>
     <row r="23">
@@ -1669,31 +1669,31 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.31025398</v>
+        <v>0.30588223</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.2440672</v>
+        <v>0.23081879</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.23310858</v>
+        <v>0.23874566</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.2327859</v>
+        <v>0.2331724</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>0.3205567</v>
+        <v>0.3103207</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>0.66267904</v>
+        <v>0.6444375</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.26557736</v>
+        <v>0.2735054</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>0.25774561</v>
+        <v>0.25874011</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>0.26551146</v>
+        <v>0.25731729</v>
       </c>
     </row>
     <row r="24">
@@ -1718,31 +1718,31 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.35633851</v>
+        <v>0.3506791</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.36670334</v>
+        <v>0.35492278</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.25002419</v>
+        <v>0.24830669</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.34511972</v>
+        <v>0.33794674</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.35187168</v>
+        <v>0.34291324</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>0.47830636</v>
+        <v>0.48472112</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.40501373</v>
+        <v>0.39575349</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>0.41894887</v>
+        <v>0.41006312</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>0.2347202</v>
+        <v>0.23080564</v>
       </c>
     </row>
     <row r="25">
@@ -1767,31 +1767,31 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.79413974</v>
+        <v>0.79502656</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.82003572</v>
+        <v>0.81631828</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.82432563</v>
+        <v>0.82545922</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0.7907956900000001</v>
+        <v>0.79767675</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>0.81703077</v>
+        <v>0.81083422</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>0.90090077</v>
+        <v>0.9036116</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>0.80514449</v>
+        <v>0.80446563</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>0.672135</v>
+        <v>0.67913591</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>0.72274989</v>
+        <v>0.72271091</v>
       </c>
     </row>
     <row r="26">
@@ -1816,31 +1816,31 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.65501172</v>
+        <v>0.6556288</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.71348218</v>
+        <v>0.72161348</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.68298155</v>
+        <v>0.68169974</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0.6884398</v>
+        <v>0.68885034</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>0.7295096599999999</v>
+        <v>0.72333028</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>0.6675916</v>
+        <v>0.6698866999999999</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>0.6223583499999999</v>
+        <v>0.63006579</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>0.59685759</v>
+        <v>0.60045284</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>0.53887307</v>
+        <v>0.5291312500000001</v>
       </c>
     </row>
     <row r="27">
@@ -1865,31 +1865,31 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.47709017</v>
+        <v>0.47529077</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.31799006</v>
+        <v>0.31989184</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.54689154</v>
+        <v>0.55667459</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0.40673951</v>
+        <v>0.40162178</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>0.24904997</v>
+        <v>0.24884982</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>0.81102681</v>
+        <v>0.79701878</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>0.51094673</v>
+        <v>0.51094287</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>0.5275520500000001</v>
+        <v>0.51930961</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>0.44652469</v>
+        <v>0.44801683</v>
       </c>
     </row>
     <row r="28">
@@ -1914,31 +1914,31 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.47184299</v>
+        <v>0.45995923</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.49277824</v>
+        <v>0.49958655</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.39030435</v>
+        <v>0.3756424</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.60815661</v>
+        <v>0.5948441</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>0.49699696</v>
+        <v>0.5011790699999999</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0.49919627</v>
+        <v>0.4583966</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>0.52227127</v>
+        <v>0.50286088</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>0.45160811</v>
+        <v>0.44699434</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>0.31343209</v>
+        <v>0.3001699</v>
       </c>
     </row>
     <row r="29">
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.33908811</v>
+        <v>0.33207129</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.38903257</v>
+        <v>0.38036592</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.1749982</v>
+        <v>0.18557636</v>
       </c>
       <c r="H29" s="5" t="n">
-        <v>0.33225393</v>
+        <v>0.32723733</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>0.38845983</v>
+        <v>0.37827095</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>0.44499543</v>
+        <v>0.3893305</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>0.35221202</v>
+        <v>0.35757892</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>0.35369665</v>
+        <v>0.35478726</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>0.27705628</v>
+        <v>0.28342311</v>
       </c>
     </row>
     <row r="30">
@@ -2012,31 +2012,31 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0.39952319</v>
+        <v>0.39342147</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.36036171</v>
+        <v>0.35696136</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.30541486</v>
+        <v>0.29344562</v>
       </c>
       <c r="H30" s="5" t="n">
-        <v>0.31784494</v>
+        <v>0.30752853</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>0.39307453</v>
+        <v>0.39385725</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>0.6180666500000001</v>
+        <v>0.60896335</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>0.43121083</v>
+        <v>0.41926605</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>0.43508206</v>
+        <v>0.43360605</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>0.33512992</v>
+        <v>0.33374358</v>
       </c>
     </row>
     <row r="31">
@@ -2061,31 +2061,31 @@
         </is>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.6756357200000001</v>
+        <v>0.6675532199999999</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.75186674</v>
+        <v>0.72431407</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.6364529799999999</v>
+        <v>0.63812146</v>
       </c>
       <c r="H31" s="5" t="n">
-        <v>0.68747639</v>
+        <v>0.6794649</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>0.76735547</v>
+        <v>0.74086096</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>0.69724423</v>
+        <v>0.70181686</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>0.68328841</v>
+        <v>0.68310286</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>0.61188406</v>
+        <v>0.61123182</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>0.56951745</v>
+        <v>0.5615128700000001</v>
       </c>
     </row>
     <row r="32">
@@ -2110,31 +2110,31 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.44405588</v>
+        <v>0.44247908</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.37305605</v>
+        <v>0.3709829</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.34053399</v>
+        <v>0.33523892</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0.34762226</v>
+        <v>0.34243437</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>0.45014387</v>
+        <v>0.44458254</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>0.6735638900000001</v>
+        <v>0.67103358</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>0.5083374000000001</v>
+        <v>0.50723956</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>0.50364842</v>
+        <v>0.51200316</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>0.35554116</v>
+        <v>0.3563176</v>
       </c>
     </row>
     <row r="33">
@@ -2159,31 +2159,31 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.60745101</v>
+        <v>0.61286628</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.56934757</v>
+        <v>0.57707926</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.56416064</v>
+        <v>0.5812507099999999</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.5967714</v>
+        <v>0.60852672</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>0.67894807</v>
+        <v>0.68854784</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>0.83606818</v>
+        <v>0.83777769</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>0.55602693</v>
+        <v>0.55206303</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>0.55657854</v>
+        <v>0.55468054</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>0.50170678</v>
+        <v>0.50300447</v>
       </c>
     </row>
     <row r="34">
@@ -2208,31 +2208,31 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.67323453</v>
+        <v>0.67366534</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.67035363</v>
+        <v>0.6653102400000001</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.65051941</v>
+        <v>0.65260416</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0.60165728</v>
+        <v>0.62753614</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.72717778</v>
+        <v>0.72141247</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>0.79747355</v>
+        <v>0.79141241</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>0.65170545</v>
+        <v>0.65619218</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>0.61651512</v>
+        <v>0.6248687000000001</v>
       </c>
       <c r="M34" s="5" t="n">
-        <v>0.6704740300000001</v>
+        <v>0.6499864400000001</v>
       </c>
     </row>
     <row r="35">
@@ -2257,31 +2257,31 @@
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.73902408</v>
+        <v>0.73131468</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.74445963</v>
+        <v>0.72692985</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.6866473400000001</v>
+        <v>0.67451269</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0.71090667</v>
+        <v>0.69802763</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>0.78354673</v>
+        <v>0.77719855</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>0.88921611</v>
+        <v>0.88707979</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>0.70470725</v>
+        <v>0.69958199</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>0.6893719</v>
+        <v>0.68503608</v>
       </c>
       <c r="M35" s="5" t="n">
-        <v>0.70333701</v>
+        <v>0.70215089</v>
       </c>
     </row>
     <row r="36">
@@ -2306,31 +2306,31 @@
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.89786373</v>
+        <v>0.8975093200000001</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.94212046</v>
+        <v>0.94772374</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.9483888700000001</v>
+        <v>0.95067012</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0.85197563</v>
+        <v>0.83868827</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>0.91355264</v>
+        <v>0.91964024</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>0.9317384</v>
+        <v>0.93267441</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0.894298</v>
+        <v>0.89031713</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.86148857</v>
+        <v>0.852361</v>
       </c>
       <c r="M36" s="5" t="n">
-        <v>0.83934728</v>
+        <v>0.8479996400000001</v>
       </c>
     </row>
     <row r="37">
@@ -2355,31 +2355,31 @@
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.57679435</v>
+        <v>0.57033802</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.52365228</v>
+        <v>0.52553161</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.61181266</v>
+        <v>0.60461688</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.49112147</v>
+        <v>0.48002684</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>0.63005852</v>
+        <v>0.63462501</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>0.71358327</v>
+        <v>0.70334935</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>0.53158197</v>
+        <v>0.5146217199999999</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>0.55540457</v>
+        <v>0.55331748</v>
       </c>
       <c r="M37" s="5" t="n">
-        <v>0.5571401</v>
+        <v>0.54661528</v>
       </c>
     </row>
     <row r="38">
@@ -2404,31 +2404,31 @@
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0.50376138</v>
+        <v>0.50204238</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.52710771</v>
+        <v>0.51329468</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.41786362</v>
+        <v>0.40488341</v>
       </c>
       <c r="H38" s="5" t="n">
-        <v>0.57528627</v>
+        <v>0.58254219</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>0.58061304</v>
+        <v>0.57726307</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>0.64340918</v>
+        <v>0.6454624799999999</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>0.43999536</v>
+        <v>0.45251436</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>0.45282052</v>
+        <v>0.44681781</v>
       </c>
       <c r="M38" s="5" t="n">
-        <v>0.39299531</v>
+        <v>0.39356107</v>
       </c>
     </row>
     <row r="39">
@@ -2453,31 +2453,31 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.45550633</v>
+        <v>0.44564789</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0.50066619</v>
+        <v>0.48963198</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.35997695</v>
+        <v>0.3475757</v>
       </c>
       <c r="H39" s="5" t="n">
-        <v>0.51760496</v>
+        <v>0.50539691</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>0.5154083</v>
+        <v>0.48906711</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>0.56975764</v>
+        <v>0.5663755700000001</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>0.45117835</v>
+        <v>0.45893256</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>0.43410632</v>
+        <v>0.42310672</v>
       </c>
       <c r="M39" s="5" t="n">
-        <v>0.29535195</v>
+        <v>0.28509658</v>
       </c>
     </row>
     <row r="40">
@@ -2502,31 +2502,31 @@
         </is>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.34621281</v>
+        <v>0.34785562</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.23077249</v>
+        <v>0.22784324</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.37528615</v>
+        <v>0.37638911</v>
       </c>
       <c r="H40" s="5" t="n">
-        <v>0.22683576</v>
+        <v>0.23236606</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0.2290842</v>
+        <v>0.22628571</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>0.65106509</v>
+        <v>0.64955081</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>0.34878952</v>
+        <v>0.35558472</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.37120947</v>
+        <v>0.37418475</v>
       </c>
       <c r="M40" s="5" t="n">
-        <v>0.33665982</v>
+        <v>0.34064054</v>
       </c>
     </row>
     <row r="41">
@@ -2551,31 +2551,31 @@
         </is>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.41992069</v>
+        <v>0.41635861</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.35292423</v>
+        <v>0.34587063</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.33757124</v>
+        <v>0.35040851</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0.42147317</v>
+        <v>0.41447899</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>0.41331303</v>
+        <v>0.39206596</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>0.71026741</v>
+        <v>0.70985588</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>0.45257184</v>
+        <v>0.44774061</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.46825715</v>
+        <v>0.46991918</v>
       </c>
       <c r="M41" s="5" t="n">
-        <v>0.20298746</v>
+        <v>0.20052913</v>
       </c>
     </row>
     <row r="42">
@@ -2600,31 +2600,31 @@
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.8189234399999999</v>
+        <v>0.81838767</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.82849087</v>
+        <v>0.82536568</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.82543479</v>
+        <v>0.82376774</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.80992992</v>
+        <v>0.8049141</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>0.8245307200000001</v>
+        <v>0.83290955</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>0.90725034</v>
+        <v>0.90614208</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>0.80646257</v>
+        <v>0.80256097</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>0.79138194</v>
+        <v>0.78684148</v>
       </c>
       <c r="M42" s="5" t="n">
-        <v>0.75790633</v>
+        <v>0.76459975</v>
       </c>
     </row>
     <row r="43">
@@ -2649,31 +2649,31 @@
         </is>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.36220672</v>
+        <v>0.35751074</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.31427355</v>
+        <v>0.29918759</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.40395447</v>
+        <v>0.39830733</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>0.30110913</v>
+        <v>0.28103447</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>0.27426522</v>
+        <v>0.26610124</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>0.5168674</v>
+        <v>0.51991494</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>0.34590213</v>
+        <v>0.35117873</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>0.39961446</v>
+        <v>0.41203991</v>
       </c>
       <c r="M43" s="5" t="n">
-        <v>0.34166739</v>
+        <v>0.33232169</v>
       </c>
     </row>
     <row r="44">
@@ -2698,31 +2698,31 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.8707053</v>
+        <v>0.87002844</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.91540457</v>
+        <v>0.91630308</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.89846278</v>
+        <v>0.8994981</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.84343645</v>
+        <v>0.8419658</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>0.89564647</v>
+        <v>0.89948721</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>0.92266933</v>
+        <v>0.92144841</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>0.85447319</v>
+        <v>0.85091701</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>0.80029933</v>
+        <v>0.79798376</v>
       </c>
       <c r="M44" s="5" t="n">
-        <v>0.83525025</v>
+        <v>0.83262413</v>
       </c>
     </row>
     <row r="45">
@@ -2747,31 +2747,31 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0.72377548</v>
+        <v>0.71631585</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.7198217099999999</v>
+        <v>0.70656147</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.75208506</v>
+        <v>0.73778185</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.74866073</v>
+        <v>0.73859776</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>0.73333266</v>
+        <v>0.72274335</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>0.78802417</v>
+        <v>0.78511445</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>0.73720916</v>
+        <v>0.73553724</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>0.67032876</v>
+        <v>0.66817299</v>
       </c>
       <c r="M45" s="5" t="n">
-        <v>0.64074157</v>
+        <v>0.6360177299999999</v>
       </c>
     </row>
     <row r="46">
@@ -2796,31 +2796,31 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.40204301</v>
+        <v>0.40313</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.31563168</v>
+        <v>0.30716941</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.25659982</v>
+        <v>0.25885945</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0.38264738</v>
+        <v>0.37827061</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>0.44328188</v>
+        <v>0.44337401</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>0.6494891</v>
+        <v>0.65094898</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>0.46464347</v>
+        <v>0.4613734</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>0.40205761</v>
+        <v>0.42281886</v>
       </c>
       <c r="M46" s="5" t="n">
-        <v>0.3019931</v>
+        <v>0.30222527</v>
       </c>
     </row>
     <row r="47">
@@ -2845,31 +2845,31 @@
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.48625897</v>
+        <v>0.48773879</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.55476645</v>
+        <v>0.55925857</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.47149086</v>
+        <v>0.46756398</v>
       </c>
       <c r="H47" s="5" t="n">
-        <v>0.39104626</v>
+        <v>0.3925157</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>0.5002544799999999</v>
+        <v>0.5066427</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>0.6915814300000001</v>
+        <v>0.69050911</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>0.37084076</v>
+        <v>0.36978373</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>0.50574436</v>
+        <v>0.50929602</v>
       </c>
       <c r="M47" s="5" t="n">
-        <v>0.40434718</v>
+        <v>0.40634053</v>
       </c>
     </row>
     <row r="48">
@@ -2894,31 +2894,31 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.5811493599999999</v>
+        <v>0.56951703</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.48796216</v>
+        <v>0.47377283</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.6504031300000001</v>
+        <v>0.63498371</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>0.57255629</v>
+        <v>0.56575399</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>0.56987095</v>
+        <v>0.55489901</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>0.78292269</v>
+        <v>0.78188563</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>0.56875057</v>
+        <v>0.56761701</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>0.5197126399999999</v>
+        <v>0.49696614</v>
       </c>
       <c r="M48" s="5" t="n">
-        <v>0.49701646</v>
+        <v>0.48025788</v>
       </c>
     </row>
     <row r="49">
@@ -2943,31 +2943,31 @@
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.8333243</v>
+        <v>0.82955386</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.85860509</v>
+        <v>0.85298631</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.83311309</v>
+        <v>0.83164017</v>
       </c>
       <c r="H49" s="5" t="n">
-        <v>0.78815375</v>
+        <v>0.7789595</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>0.8625966900000001</v>
+        <v>0.85349028</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>0.87831395</v>
+        <v>0.8824403199999999</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>0.83523409</v>
+        <v>0.8284318899999999</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>0.81968912</v>
+        <v>0.81795162</v>
       </c>
       <c r="M49" s="5" t="n">
-        <v>0.79088862</v>
+        <v>0.7905308</v>
       </c>
     </row>
     <row r="50">
@@ -2992,31 +2992,31 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.54499807</v>
+        <v>0.54753724</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.65536091</v>
+        <v>0.65870262</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.38334479</v>
+        <v>0.38718245</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0.51402653</v>
+        <v>0.51980572</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>0.572843</v>
+        <v>0.57511378</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>0.7137738300000001</v>
+        <v>0.71520841</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>0.52153433</v>
+        <v>0.51622975</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>0.5515569299999999</v>
+        <v>0.55640735</v>
       </c>
       <c r="M50" s="5" t="n">
-        <v>0.4475442</v>
+        <v>0.45164783</v>
       </c>
     </row>
     <row r="51">
@@ -3041,31 +3041,31 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.59691846</v>
+        <v>0.60060821</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.63484547</v>
+        <v>0.64364381</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.56185423</v>
+        <v>0.5666512500000001</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>0.5937584299999999</v>
+        <v>0.60127427</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>0.63273159</v>
+        <v>0.63534154</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>0.72012458</v>
+        <v>0.71890834</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>0.55527455</v>
+        <v>0.5608066900000001</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>0.57771345</v>
+        <v>0.58502131</v>
       </c>
       <c r="M51" s="5" t="n">
-        <v>0.49904538</v>
+        <v>0.49321846</v>
       </c>
     </row>
     <row r="52">
@@ -3090,31 +3090,31 @@
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0.59669006</v>
+        <v>0.59252136</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.5807889899999999</v>
+        <v>0.57536768</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.65150096</v>
+        <v>0.6379257</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0.4592028</v>
+        <v>0.45159151</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>0.62504116</v>
+        <v>0.61601416</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>0.77806906</v>
+        <v>0.78830297</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>0.54049303</v>
+        <v>0.53587481</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>0.60124015</v>
+        <v>0.5967452</v>
       </c>
       <c r="M52" s="5" t="n">
-        <v>0.53718437</v>
+        <v>0.53834887</v>
       </c>
     </row>
     <row r="53">
@@ -3139,31 +3139,31 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>0.43949764</v>
+        <v>0.44418736</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>0.48582484</v>
+        <v>0.49069365</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.35118503</v>
+        <v>0.35977719</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>0.52454196</v>
+        <v>0.5275797</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>0.53059703</v>
+        <v>0.52587567</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>0.5854800999999999</v>
+        <v>0.59114165</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>0.40846965</v>
+        <v>0.41703637</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>0.3287606</v>
+        <v>0.33504193</v>
       </c>
       <c r="M53" s="5" t="n">
-        <v>0.30112188</v>
+        <v>0.30635273</v>
       </c>
     </row>
     <row r="54">
@@ -3188,31 +3188,31 @@
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0.40879427</v>
+        <v>0.40395772</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>0.36515733</v>
+        <v>0.3558282</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.29586913</v>
+        <v>0.29636982</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>0.35532659</v>
+        <v>0.34095508</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>0.48435328</v>
+        <v>0.47392776</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>0.72348947</v>
+        <v>0.72288112</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>0.35821831</v>
+        <v>0.35382094</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>0.37933641</v>
+        <v>0.37668053</v>
       </c>
       <c r="M54" s="5" t="n">
-        <v>0.30860361</v>
+        <v>0.31119829</v>
       </c>
     </row>
     <row r="55">
@@ -3237,31 +3237,31 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>0.49976778</v>
+        <v>0.49748912</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.52774526</v>
+        <v>0.52707087</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.45288902</v>
+        <v>0.45231682</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>0.44087122</v>
+        <v>0.43502612</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>0.54828603</v>
+        <v>0.54051658</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>0.6287333000000001</v>
+        <v>0.62772815</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>0.47131251</v>
+        <v>0.47887833</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>0.5269982600000001</v>
+        <v>0.51680439</v>
       </c>
       <c r="M55" s="5" t="n">
-        <v>0.40130665</v>
+        <v>0.40157169</v>
       </c>
     </row>
     <row r="56">
@@ -3286,31 +3286,31 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0.32376015</v>
+        <v>0.30554575</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.3425375</v>
+        <v>0.33088846</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.2392065</v>
+        <v>0.22513847</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>0.3296067</v>
+        <v>0.32131172</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>0.42445191</v>
+        <v>0.41263976</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>0.42633342</v>
+        <v>0.36359783</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>0.26177504</v>
+        <v>0.26136178</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>0.32735634</v>
+        <v>0.31060434</v>
       </c>
       <c r="M56" s="5" t="n">
-        <v>0.23881381</v>
+        <v>0.21882368</v>
       </c>
     </row>
     <row r="57">
@@ -3335,31 +3335,31 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>0.41139412</v>
+        <v>0.40922723</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>0.37366058</v>
+        <v>0.37735612</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.31395855</v>
+        <v>0.31514744</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>0.44037223</v>
+        <v>0.44351636</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>0.46127606</v>
+        <v>0.46080391</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>0.63712049</v>
+        <v>0.63443836</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>0.38748111</v>
+        <v>0.37217252</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>0.40394807</v>
+        <v>0.39039472</v>
       </c>
       <c r="M57" s="5" t="n">
-        <v>0.27333592</v>
+        <v>0.27998841</v>
       </c>
     </row>
     <row r="58">
@@ -3384,31 +3384,31 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0.71824242</v>
+        <v>0.71049727</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.54969374</v>
+        <v>0.53928441</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.8439279200000001</v>
+        <v>0.83381648</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>0.68034615</v>
+        <v>0.67187338</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>0.56891303</v>
+        <v>0.55307187</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>0.92265403</v>
+        <v>0.92275402</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>0.79435351</v>
+        <v>0.79184076</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>0.70471538</v>
+        <v>0.6991482</v>
       </c>
       <c r="M58" s="5" t="n">
-        <v>0.68133563</v>
+        <v>0.67218906</v>
       </c>
     </row>
     <row r="59">
@@ -3433,31 +3433,31 @@
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>0.50260437</v>
+        <v>0.5004206</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.35014158</v>
+        <v>0.35487008</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.48230236</v>
+        <v>0.48076941</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>0.44812927</v>
+        <v>0.45401239</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>0.51816358</v>
+        <v>0.5125826999999999</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>0.8868059700000001</v>
+        <v>0.88520022</v>
       </c>
       <c r="K59" s="5" t="n">
-        <v>0.44185359</v>
+        <v>0.43259571</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>0.45094691</v>
+        <v>0.4518389</v>
       </c>
       <c r="M59" s="5" t="n">
-        <v>0.44249171</v>
+        <v>0.43149538</v>
       </c>
     </row>
     <row r="60">
@@ -3482,31 +3482,31 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.48898741</v>
+        <v>0.48282309</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.55179086</v>
+        <v>0.53845444</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.39976998</v>
+        <v>0.40444377</v>
       </c>
       <c r="H60" s="5" t="n">
-        <v>0.58615286</v>
+        <v>0.5797588299999999</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>0.44977591</v>
+        <v>0.44328657</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>0.64134074</v>
+        <v>0.61198963</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>0.47870896</v>
+        <v>0.48042407</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>0.41898981</v>
+        <v>0.41631015</v>
       </c>
       <c r="M60" s="5" t="n">
-        <v>0.38537018</v>
+        <v>0.38791722</v>
       </c>
     </row>
     <row r="61">
@@ -3531,31 +3531,31 @@
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0.52387695</v>
+        <v>0.51208222</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.62071422</v>
+        <v>0.60436776</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.42205791</v>
+        <v>0.41796206</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>0.54637378</v>
+        <v>0.53771482</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>0.46897225</v>
+        <v>0.44525944</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>0.70666121</v>
+        <v>0.70459417</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>0.57977821</v>
+        <v>0.57272657</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>0.46705748</v>
+        <v>0.44450518</v>
       </c>
       <c r="M61" s="5" t="n">
-        <v>0.37940051</v>
+        <v>0.36952778</v>
       </c>
     </row>
     <row r="62">
@@ -3580,31 +3580,31 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0.38246528</v>
+        <v>0.37369417</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0.32491677</v>
+        <v>0.32491676</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.37689563</v>
+        <v>0.37696001</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>0.27312579</v>
+        <v>0.27309745</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>0.19955822</v>
+        <v>0.2000638</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>0.61061645</v>
+        <v>0.53989628</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>0.43029205</v>
+        <v>0.43080526</v>
       </c>
       <c r="L62" s="5" t="n">
         <v>0.5080892299999999</v>
       </c>
       <c r="M62" s="5" t="n">
-        <v>0.33622811</v>
+        <v>0.33572459</v>
       </c>
     </row>
     <row r="63">
@@ -3629,31 +3629,31 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0.8234931</v>
+        <v>0.82464838</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.8413370100000001</v>
+        <v>0.83782996</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.82261791</v>
+        <v>0.83516006</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>0.82815388</v>
+        <v>0.8307907</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>0.84962021</v>
+        <v>0.84587523</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>0.93180724</v>
+        <v>0.93128419</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>0.84155552</v>
+        <v>0.8531466</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>0.73531013</v>
+        <v>0.72790026</v>
       </c>
       <c r="M63" s="5" t="n">
-        <v>0.7375429100000001</v>
+        <v>0.73520002</v>
       </c>
     </row>
     <row r="64">
@@ -3678,31 +3678,31 @@
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>0.6565117499999999</v>
+        <v>0.65535474</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.7023313</v>
+        <v>0.69379632</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.64936898</v>
+        <v>0.64684235</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>0.636892</v>
+        <v>0.64424998</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>0.71508775</v>
+        <v>0.7042524999999999</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>0.7490926</v>
+        <v>0.74844466</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>0.61123522</v>
+        <v>0.61531739</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>0.56288955</v>
+        <v>0.56854907</v>
       </c>
       <c r="M64" s="5" t="n">
-        <v>0.62519663</v>
+        <v>0.62138563</v>
       </c>
     </row>
     <row r="65">
@@ -3727,31 +3727,31 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0.56986124</v>
+        <v>0.56684945</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>0.63302375</v>
+        <v>0.62303642</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.53592674</v>
+        <v>0.52927791</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0.55118724</v>
+        <v>0.54484887</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>0.64129244</v>
+        <v>0.63947279</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>0.62088811</v>
+        <v>0.6208919000000001</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>0.53692432</v>
+        <v>0.53776086</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>0.55726532</v>
+        <v>0.55993284</v>
       </c>
       <c r="M65" s="5" t="n">
-        <v>0.48238201</v>
+        <v>0.47957399</v>
       </c>
     </row>
     <row r="66">
@@ -3776,31 +3776,31 @@
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>0.78367491</v>
+        <v>0.78247422</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.72149353</v>
+        <v>0.7203098100000001</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.82190558</v>
+        <v>0.81802169</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>0.70588037</v>
+        <v>0.70116926</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>0.77932675</v>
+        <v>0.7783343</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>0.92846935</v>
+        <v>0.92982299</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>0.792494</v>
+        <v>0.79907522</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>0.75907875</v>
+        <v>0.75370414</v>
       </c>
       <c r="M66" s="5" t="n">
-        <v>0.76075096</v>
+        <v>0.75935631</v>
       </c>
     </row>
     <row r="67">
@@ -3821,35 +3821,35 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Lower-middle</t>
+          <t>Upper-middle</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0.55158001</v>
+        <v>0.55150486</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.47622664</v>
+        <v>0.47461441</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.59069339</v>
+        <v>0.5986196499999999</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>0.38584149</v>
+        <v>0.38421457</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>0.45644349</v>
+        <v>0.46143397</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>0.76138887</v>
+        <v>0.7574506600000001</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>0.57050822</v>
+        <v>0.56810172</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>0.61207776</v>
+        <v>0.6066167099999999</v>
       </c>
       <c r="M67" s="5" t="n">
-        <v>0.5594602400000001</v>
+        <v>0.5609872</v>
       </c>
     </row>
     <row r="68">
@@ -3874,31 +3874,31 @@
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>0.5363161</v>
+        <v>0.52873666</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.46030614</v>
+        <v>0.45012585</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.485161</v>
+        <v>0.47463339</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>0.47517344</v>
+        <v>0.46833532</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>0.4609544</v>
+        <v>0.44814461</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>0.80356841</v>
+        <v>0.80371633</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>0.52544564</v>
+        <v>0.5223186</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>0.6164696</v>
+        <v>0.61045122</v>
       </c>
       <c r="M68" s="5" t="n">
-        <v>0.46345019</v>
+        <v>0.452168</v>
       </c>
     </row>
     <row r="69">
@@ -3923,31 +3923,31 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0.4506896</v>
+        <v>0.44719104</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.46713306</v>
+        <v>0.46139536</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.26210352</v>
+        <v>0.25759741</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>0.5015771</v>
+        <v>0.49440824</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>0.47581797</v>
+        <v>0.46396271</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>0.55283706</v>
+        <v>0.56087448</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>0.45192541</v>
+        <v>0.44870715</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>0.50054585</v>
+        <v>0.50194418</v>
       </c>
       <c r="M69" s="5" t="n">
-        <v>0.39357686</v>
+        <v>0.38863881</v>
       </c>
     </row>
     <row r="70">
@@ -3972,31 +3972,31 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>0.74324292</v>
+        <v>0.74340978</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.7131894</v>
+        <v>0.71333213</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.6711012200000001</v>
+        <v>0.66720165</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.73114774</v>
+        <v>0.7322497100000001</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>0.75332139</v>
+        <v>0.75647163</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>0.85118876</v>
+        <v>0.855223</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>0.74686949</v>
+        <v>0.74709431</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>0.75725754</v>
+        <v>0.75474165</v>
       </c>
       <c r="M70" s="5" t="n">
-        <v>0.72186779</v>
+        <v>0.72096419</v>
       </c>
     </row>
     <row r="71">
@@ -4021,31 +4021,31 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0.5609856600000001</v>
+        <v>0.55907529</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.56470803</v>
+        <v>0.55407122</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.48756579</v>
+        <v>0.49109014</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>0.56521527</v>
+        <v>0.57073198</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>0.61020634</v>
+        <v>0.60688878</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>0.83578114</v>
+        <v>0.8408596</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>0.46792317</v>
+        <v>0.46749343</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>0.48704056</v>
+        <v>0.48798151</v>
       </c>
       <c r="M71" s="5" t="n">
-        <v>0.469445</v>
+        <v>0.45348569</v>
       </c>
     </row>
     <row r="72">
@@ -4070,31 +4070,31 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>0.57898735</v>
+        <v>0.5817618</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.5171461000000001</v>
+        <v>0.5227191799999999</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.68333407</v>
+        <v>0.68192148</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>0.42469292</v>
+        <v>0.42414254</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>0.44318489</v>
+        <v>0.44254396</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>0.8794845100000001</v>
+        <v>0.88536458</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>0.65274363</v>
+        <v>0.65774444</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>0.5746436700000001</v>
+        <v>0.56663314</v>
       </c>
       <c r="M72" s="5" t="n">
-        <v>0.456669</v>
+        <v>0.47302509</v>
       </c>
     </row>
     <row r="73">
@@ -4119,31 +4119,31 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0.44826869</v>
+        <v>0.44802649</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.42158276</v>
+        <v>0.42328392</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.29416536</v>
+        <v>0.29955134</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.48492996</v>
+        <v>0.48009377</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>0.44468789</v>
+        <v>0.43432801</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>0.75532237</v>
+        <v>0.75421289</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>0.40282576</v>
+        <v>0.40598468</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>0.4656105</v>
+        <v>0.46343743</v>
       </c>
       <c r="M73" s="5" t="n">
-        <v>0.31702488</v>
+        <v>0.32331986</v>
       </c>
     </row>
     <row r="74">
@@ -4168,31 +4168,31 @@
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>0.73348182</v>
+        <v>0.74538483</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>0.70268124</v>
+        <v>0.72425627</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.6914927400000001</v>
+        <v>0.7097765</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>0.73404705</v>
+        <v>0.73927588</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>0.76576175</v>
+        <v>0.78606734</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>0.86346981</v>
+        <v>0.86227921</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>0.72029816</v>
+        <v>0.72746756</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>0.71478979</v>
+        <v>0.72484298</v>
       </c>
       <c r="M74" s="5" t="n">
-        <v>0.67531399</v>
+        <v>0.68911288</v>
       </c>
     </row>
     <row r="75">
@@ -4217,31 +4217,31 @@
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>0.44185147</v>
+        <v>0.4408172</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>0.49118825</v>
+        <v>0.49082728</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.36862129</v>
+        <v>0.36842849</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>0.44923372</v>
+        <v>0.44827415</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>0.47426482</v>
+        <v>0.47538716</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>0.59452595</v>
+        <v>0.58658944</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>0.4369384</v>
+        <v>0.43807349</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>0.39854964</v>
+        <v>0.39803944</v>
       </c>
       <c r="M75" s="5" t="n">
-        <v>0.3214897</v>
+        <v>0.32091813</v>
       </c>
     </row>
     <row r="76">
@@ -4266,31 +4266,31 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>0.44144825</v>
+        <v>0.44558981</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.49960451</v>
+        <v>0.5065186</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.31281091</v>
+        <v>0.31808347</v>
       </c>
       <c r="H76" s="5" t="n">
-        <v>0.45583237</v>
+        <v>0.45682971</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>0.50843354</v>
+        <v>0.50740576</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>0.60678565</v>
+        <v>0.61238188</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>0.4114691</v>
+        <v>0.41478253</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>0.41023764</v>
+        <v>0.41842023</v>
       </c>
       <c r="M76" s="5" t="n">
-        <v>0.32641227</v>
+        <v>0.33029626</v>
       </c>
     </row>
     <row r="77">
@@ -4315,31 +4315,31 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0.77418824</v>
+        <v>0.77922247</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>0.76386298</v>
+        <v>0.76734997</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.75492808</v>
+        <v>0.7637591</v>
       </c>
       <c r="H77" s="5" t="n">
-        <v>0.75302326</v>
+        <v>0.75117931</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>0.78882573</v>
+        <v>0.80222651</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>0.90175256</v>
+        <v>0.89966557</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>0.76176266</v>
+        <v>0.76650763</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>0.77116479</v>
+        <v>0.77416319</v>
       </c>
       <c r="M77" s="5" t="n">
-        <v>0.69818589</v>
+        <v>0.70892847</v>
       </c>
     </row>
     <row r="78">
@@ -4364,31 +4364,31 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0.82977847</v>
+        <v>0.83134082</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.82254317</v>
+        <v>0.8260311</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.84780752</v>
+        <v>0.85682518</v>
       </c>
       <c r="H78" s="5" t="n">
-        <v>0.81003201</v>
+        <v>0.81008265</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>0.84962647</v>
+        <v>0.86067707</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>0.9517787599999999</v>
+        <v>0.93647582</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>0.84799533</v>
+        <v>0.84164068</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>0.77483742</v>
+        <v>0.77577889</v>
       </c>
       <c r="M78" s="5" t="n">
-        <v>0.73360709</v>
+        <v>0.74321515</v>
       </c>
     </row>
     <row r="79">
@@ -4413,31 +4413,31 @@
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>0.43209549</v>
+        <v>0.42798209</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.41431639</v>
+        <v>0.40796797</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.27384885</v>
+        <v>0.26925943</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>0.44302972</v>
+        <v>0.44402253</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>0.46306822</v>
+        <v>0.44907369</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>0.71129986</v>
+        <v>0.71379417</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>0.39989461</v>
+        <v>0.39859352</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>0.4260778</v>
+        <v>0.42485293</v>
       </c>
       <c r="M79" s="5" t="n">
-        <v>0.32522844</v>
+        <v>0.31629252</v>
       </c>
     </row>
     <row r="80">
@@ -4462,31 +4462,31 @@
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>0.51987902</v>
+        <v>0.52279984</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.5699184</v>
+        <v>0.5723361</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.41856666</v>
+        <v>0.42516716</v>
       </c>
       <c r="H80" s="5" t="n">
-        <v>0.45649742</v>
+        <v>0.47102376</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>0.5733329</v>
+        <v>0.5771272200000001</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>0.67664286</v>
+        <v>0.67504237</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>0.47102785</v>
+        <v>0.46735954</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0.55858703</v>
+        <v>0.54976688</v>
       </c>
       <c r="M80" s="5" t="n">
-        <v>0.43445901</v>
+        <v>0.44457571</v>
       </c>
     </row>
     <row r="81">
@@ -4511,31 +4511,31 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>0.56995633</v>
+        <v>0.57324176</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>0.56383712</v>
+        <v>0.5723745</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.56744801</v>
+        <v>0.55875902</v>
       </c>
       <c r="H81" s="5" t="n">
-        <v>0.4107739</v>
+        <v>0.41646136</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>0.50078922</v>
+        <v>0.51331309</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>0.77868872</v>
+        <v>0.7784835</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>0.56398911</v>
+        <v>0.57463689</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>0.61791282</v>
+        <v>0.61330482</v>
       </c>
       <c r="M81" s="5" t="n">
-        <v>0.55621174</v>
+        <v>0.5586009199999999</v>
       </c>
     </row>
     <row r="82">
@@ -4560,31 +4560,31 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0.38519028</v>
+        <v>0.37744059</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>0.39681091</v>
+        <v>0.37258749</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.30898245</v>
+        <v>0.31328393</v>
       </c>
       <c r="H82" s="5" t="n">
-        <v>0.43107466</v>
+        <v>0.41806857</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>0.45110581</v>
+        <v>0.44088692</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>0.36896001</v>
+        <v>0.37348529</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>0.45550435</v>
+        <v>0.44777955</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>0.3883163</v>
+        <v>0.37901097</v>
       </c>
       <c r="M82" s="5" t="n">
-        <v>0.28076772</v>
+        <v>0.27442197</v>
       </c>
     </row>
     <row r="83">
@@ -4609,31 +4609,31 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0.66978317</v>
+        <v>0.66865013</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>0.61201467</v>
+        <v>0.58945319</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.64383757</v>
+        <v>0.6398119799999999</v>
       </c>
       <c r="H83" s="5" t="n">
-        <v>0.63290382</v>
+        <v>0.6223705</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>0.74252736</v>
+        <v>0.74117081</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>0.91108555</v>
+        <v>0.91698185</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>0.58203194</v>
+        <v>0.59121795</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>0.6011531</v>
+        <v>0.60974797</v>
       </c>
       <c r="M83" s="5" t="n">
-        <v>0.63271134</v>
+        <v>0.63844681</v>
       </c>
     </row>
     <row r="84">
@@ -4658,31 +4658,31 @@
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0.36177795</v>
+        <v>0.36111784</v>
       </c>
       <c r="F84" s="5" t="n">
-        <v>0.33734554</v>
+        <v>0.33189745</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.30577094</v>
+        <v>0.30701568</v>
       </c>
       <c r="H84" s="5" t="n">
-        <v>0.28654734</v>
+        <v>0.28225034</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>0.37227144</v>
+        <v>0.37033035</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>0.6398962</v>
+        <v>0.6346569</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>0.28532302</v>
+        <v>0.28856325</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>0.39892097</v>
+        <v>0.40021143</v>
       </c>
       <c r="M84" s="5" t="n">
-        <v>0.26814819</v>
+        <v>0.27401729</v>
       </c>
     </row>
     <row r="85">
@@ -4707,31 +4707,31 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0.60351942</v>
+        <v>0.60002588</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>0.5776052699999999</v>
+        <v>0.58146802</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.57889691</v>
+        <v>0.56514904</v>
       </c>
       <c r="H85" s="5" t="n">
-        <v>0.51666079</v>
+        <v>0.52179504</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>0.63371426</v>
+        <v>0.63575015</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>0.75307917</v>
+        <v>0.75297656</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>0.6224079</v>
+        <v>0.61371941</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>0.60946743</v>
+        <v>0.59865759</v>
       </c>
       <c r="M85" s="5" t="n">
-        <v>0.53632364</v>
+        <v>0.53069126</v>
       </c>
     </row>
     <row r="86">
@@ -4756,31 +4756,31 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>0.40311297</v>
+        <v>0.392074</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>0.40670966</v>
+        <v>0.39445847</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.27093791</v>
+        <v>0.26105321</v>
       </c>
       <c r="H86" s="5" t="n">
-        <v>0.5564020200000001</v>
+        <v>0.54131497</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>0.46631006</v>
+        <v>0.46020313</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>0.50019806</v>
+        <v>0.5018038</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>0.42272125</v>
+        <v>0.41182347</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>0.35238696</v>
+        <v>0.34123799</v>
       </c>
       <c r="M86" s="5" t="n">
-        <v>0.24923783</v>
+        <v>0.22469697</v>
       </c>
     </row>
     <row r="87">
@@ -4805,31 +4805,31 @@
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0.5304462</v>
+        <v>0.53196627</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0.51644634</v>
+        <v>0.51388836</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.36548384</v>
+        <v>0.3798033</v>
       </c>
       <c r="H87" s="5" t="n">
-        <v>0.56648098</v>
+        <v>0.56452326</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>0.60781361</v>
+        <v>0.60364693</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>0.81749891</v>
+        <v>0.82100857</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>0.45817607</v>
+        <v>0.45794344</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>0.48516786</v>
+        <v>0.47599938</v>
       </c>
       <c r="M87" s="5" t="n">
-        <v>0.42650201</v>
+        <v>0.4389169</v>
       </c>
     </row>
     <row r="88">
@@ -4854,31 +4854,31 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>0.53220495</v>
+        <v>0.5251277</v>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0.52719299</v>
+        <v>0.52047359</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.41829598</v>
+        <v>0.40990631</v>
       </c>
       <c r="H88" s="5" t="n">
-        <v>0.48522149</v>
+        <v>0.48149595</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>0.55991366</v>
+        <v>0.5534988</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>0.76241648</v>
+        <v>0.7622193</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>0.48146871</v>
+        <v>0.47126773</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>0.54083843</v>
+        <v>0.5322469</v>
       </c>
       <c r="M88" s="5" t="n">
-        <v>0.48229185</v>
+        <v>0.46991299</v>
       </c>
     </row>
     <row r="89">
@@ -4903,31 +4903,31 @@
         </is>
       </c>
       <c r="E89" s="5" t="n">
-        <v>0.57089263</v>
+        <v>0.56519188</v>
       </c>
       <c r="F89" s="5" t="n">
-        <v>0.54434648</v>
+        <v>0.52458604</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.48707705</v>
+        <v>0.48773407</v>
       </c>
       <c r="H89" s="5" t="n">
-        <v>0.54615783</v>
+        <v>0.54169008</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>0.67088167</v>
+        <v>0.67013068</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>0.81922725</v>
+        <v>0.80624159</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>0.4827861</v>
+        <v>0.47192363</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>0.54131785</v>
+        <v>0.54194522</v>
       </c>
       <c r="M89" s="5" t="n">
-        <v>0.47534678</v>
+        <v>0.47728368</v>
       </c>
     </row>
     <row r="90">
@@ -4952,31 +4952,31 @@
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>0.4806151</v>
+        <v>0.48200969</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.50541503</v>
+        <v>0.50304539</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.41692821</v>
+        <v>0.42312954</v>
       </c>
       <c r="H90" s="5" t="n">
-        <v>0.42379954</v>
+        <v>0.42600459</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>0.43183861</v>
+        <v>0.42277611</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>0.68751927</v>
+        <v>0.68926315</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>0.48939238</v>
+        <v>0.49875459</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>0.50798079</v>
+        <v>0.50969318</v>
       </c>
       <c r="M90" s="5" t="n">
-        <v>0.382047</v>
+        <v>0.38341095</v>
       </c>
     </row>
     <row r="91">
@@ -5001,31 +5001,31 @@
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0.37387315</v>
+        <v>0.37094514</v>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.38988146</v>
+        <v>0.38434596</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.33439162</v>
+        <v>0.33611206</v>
       </c>
       <c r="H91" s="5" t="n">
-        <v>0.35003407</v>
+        <v>0.34861161</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>0.38021217</v>
+        <v>0.38025998</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>0.44457156</v>
+        <v>0.41650131</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>0.37764901</v>
+        <v>0.3775469</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>0.41116061</v>
+        <v>0.41497698</v>
       </c>
       <c r="M91" s="5" t="n">
-        <v>0.30308472</v>
+        <v>0.30920631</v>
       </c>
     </row>
     <row r="92">
@@ -5050,31 +5050,31 @@
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>0.33605104</v>
+        <v>0.3295182</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>0.25198844</v>
+        <v>0.23816622</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.40290527</v>
+        <v>0.39749567</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>0.28473572</v>
+        <v>0.26985157</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>0.17814461</v>
+        <v>0.17082858</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>0.60053765</v>
+        <v>0.5998648</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>0.41249344</v>
+        <v>0.41394212</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>0.32785485</v>
+        <v>0.31898568</v>
       </c>
       <c r="M92" s="5" t="n">
-        <v>0.22974833</v>
+        <v>0.22701092</v>
       </c>
     </row>
     <row r="93">
@@ -5099,31 +5099,31 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0.60877962</v>
+        <v>0.60571449</v>
       </c>
       <c r="F93" s="5" t="n">
-        <v>0.6502084299999999</v>
+        <v>0.65086068</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.52347963</v>
+        <v>0.52513857</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>0.58059219</v>
+        <v>0.57103383</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>0.64001777</v>
+        <v>0.63834392</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>0.75391222</v>
+        <v>0.75511195</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>0.57287079</v>
+        <v>0.56662318</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>0.6078294</v>
+        <v>0.59980183</v>
       </c>
       <c r="M93" s="5" t="n">
-        <v>0.54132654</v>
+        <v>0.53880192</v>
       </c>
     </row>
     <row r="94">
@@ -5148,31 +5148,31 @@
         </is>
       </c>
       <c r="E94" s="5" t="n">
-        <v>0.5192691</v>
+        <v>0.52194781</v>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.59206221</v>
+        <v>0.58681808</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.41727607</v>
+        <v>0.42890317</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>0.50366333</v>
+        <v>0.50008951</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>0.51147363</v>
+        <v>0.51478133</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>0.7221116400000001</v>
+        <v>0.7220011</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>0.48217292</v>
+        <v>0.4858872</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>0.44193474</v>
+        <v>0.45237445</v>
       </c>
       <c r="M94" s="5" t="n">
-        <v>0.4834583</v>
+        <v>0.48472766</v>
       </c>
     </row>
     <row r="95">
@@ -5197,31 +5197,31 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0.8208597</v>
+        <v>0.82269568</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.82744786</v>
+        <v>0.83432123</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.87372656</v>
+        <v>0.87596323</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>0.80469577</v>
+        <v>0.80263403</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>0.82091739</v>
+        <v>0.82612201</v>
       </c>
       <c r="J95" s="5" t="n">
-        <v>0.8411956</v>
+        <v>0.84273315</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>0.82753878</v>
+        <v>0.82813054</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>0.82367105</v>
+        <v>0.82291905</v>
       </c>
       <c r="M95" s="5" t="n">
-        <v>0.74768458</v>
+        <v>0.74874223</v>
       </c>
     </row>
     <row r="96">
@@ -5246,31 +5246,31 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0.83394471</v>
+        <v>0.82893393</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.86077266</v>
+        <v>0.85517529</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.88501852</v>
+        <v>0.88556105</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>0.82278084</v>
+        <v>0.80371036</v>
       </c>
       <c r="I96" s="5" t="n">
-        <v>0.83579865</v>
+        <v>0.82643517</v>
       </c>
       <c r="J96" s="5" t="n">
-        <v>0.88585579</v>
+        <v>0.88956416</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>0.85188926</v>
+        <v>0.8471471</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>0.789177</v>
+        <v>0.79129815</v>
       </c>
       <c r="M96" s="5" t="n">
-        <v>0.74026495</v>
+        <v>0.73258015</v>
       </c>
     </row>
     <row r="97">
@@ -5295,31 +5295,31 @@
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0.33124185</v>
+        <v>0.32302522</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.22390126</v>
+        <v>0.21220249</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.2928971</v>
+        <v>0.29145402</v>
       </c>
       <c r="H97" s="5" t="n">
-        <v>0.2956621</v>
+        <v>0.28764015</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>0.2774494</v>
+        <v>0.26327527</v>
       </c>
       <c r="J97" s="5" t="n">
-        <v>0.69363489</v>
+        <v>0.68881856</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>0.34053425</v>
+        <v>0.34158966</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>0.28027207</v>
+        <v>0.26646837</v>
       </c>
       <c r="M97" s="5" t="n">
-        <v>0.24558373</v>
+        <v>0.23275323</v>
       </c>
     </row>
     <row r="98">
@@ -5344,31 +5344,31 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>0.41672597</v>
+        <v>0.40825131</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.36749355</v>
+        <v>0.34885495</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.38912904</v>
+        <v>0.38907111</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>0.33945303</v>
+        <v>0.32169139</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>0.4427541</v>
+        <v>0.42132489</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>0.56014439</v>
+        <v>0.5535096</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>0.45673315</v>
+        <v>0.45874305</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>0.42916193</v>
+        <v>0.42626001</v>
       </c>
       <c r="M98" s="5" t="n">
-        <v>0.34893854</v>
+        <v>0.34655545</v>
       </c>
     </row>
     <row r="99">
@@ -5393,31 +5393,31 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>0.40565446</v>
+        <v>0.40207824</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0.47796408</v>
+        <v>0.47044922</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.33350228</v>
+        <v>0.33340269</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>0.41372203</v>
+        <v>0.42094688</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>0.42022502</v>
+        <v>0.42790579</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>0.36116978</v>
+        <v>0.32049597</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>0.40481948</v>
+        <v>0.40574061</v>
       </c>
       <c r="L99" s="5" t="n">
-        <v>0.44868059</v>
+        <v>0.44485811</v>
       </c>
       <c r="M99" s="5" t="n">
-        <v>0.38515238</v>
+        <v>0.39282666</v>
       </c>
     </row>
     <row r="100">
@@ -5442,31 +5442,31 @@
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>0.54133964</v>
+        <v>0.5380971</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.49521944</v>
+        <v>0.49095878</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.47066591</v>
+        <v>0.45653894</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>0.51406825</v>
+        <v>0.52366992</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>0.62501906</v>
+        <v>0.62672415</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>0.80277014</v>
+        <v>0.79942165</v>
       </c>
       <c r="K100" s="5" t="n">
-        <v>0.46114962</v>
+        <v>0.45576097</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>0.50585794</v>
+        <v>0.49978338</v>
       </c>
       <c r="M100" s="5" t="n">
-        <v>0.45596677</v>
+        <v>0.45191903</v>
       </c>
     </row>
     <row r="101">
@@ -5491,31 +5491,31 @@
         </is>
       </c>
       <c r="E101" s="5" t="n">
-        <v>0.89026255</v>
+        <v>0.88958738</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>0.91985063</v>
+        <v>0.92010696</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.93169897</v>
+        <v>0.92959403</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>0.88246146</v>
+        <v>0.88527373</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>0.89606424</v>
+        <v>0.90018524</v>
       </c>
       <c r="J101" s="5" t="n">
-        <v>0.92584108</v>
+        <v>0.92342713</v>
       </c>
       <c r="K101" s="5" t="n">
-        <v>0.8822111500000001</v>
+        <v>0.8802548</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>0.86198824</v>
+        <v>0.85796061</v>
       </c>
       <c r="M101" s="5" t="n">
-        <v>0.82198467</v>
+        <v>0.81989656</v>
       </c>
     </row>
     <row r="102">
@@ -5540,31 +5540,31 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>0.37050436</v>
+        <v>0.36266252</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.43330151</v>
+        <v>0.42922185</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.31159806</v>
+        <v>0.30929387</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>0.39356223</v>
+        <v>0.39127143</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>0.34839086</v>
+        <v>0.35063832</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>0.35764877</v>
+        <v>0.3181249</v>
       </c>
       <c r="K102" s="5" t="n">
-        <v>0.38625976</v>
+        <v>0.37350291</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>0.38339696</v>
+        <v>0.38169341</v>
       </c>
       <c r="M102" s="5" t="n">
-        <v>0.3498767</v>
+        <v>0.34755348</v>
       </c>
     </row>
     <row r="103">
@@ -5589,31 +5589,31 @@
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0.51866469</v>
+        <v>0.51987984</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>0.53145716</v>
+        <v>0.53576301</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.41083987</v>
+        <v>0.41245185</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>0.56592142</v>
+        <v>0.5600742399999999</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>0.62988753</v>
+        <v>0.62963083</v>
       </c>
       <c r="J103" s="5" t="n">
-        <v>0.69909652</v>
+        <v>0.70042406</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>0.49543388</v>
+        <v>0.4987668</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>0.47611281</v>
+        <v>0.47320757</v>
       </c>
       <c r="M103" s="5" t="n">
-        <v>0.3405683</v>
+        <v>0.34872035</v>
       </c>
     </row>
     <row r="104">
@@ -5638,31 +5638,31 @@
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>0.453738</v>
+        <v>0.45029822</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.4799939</v>
+        <v>0.48245199</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.2836883</v>
+        <v>0.28373514</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>0.55572711</v>
+        <v>0.55310307</v>
       </c>
       <c r="I104" s="5" t="n">
-        <v>0.50139469</v>
+        <v>0.49586199</v>
       </c>
       <c r="J104" s="5" t="n">
-        <v>0.69004078</v>
+        <v>0.68531346</v>
       </c>
       <c r="K104" s="5" t="n">
-        <v>0.45269039</v>
+        <v>0.44138474</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>0.40250181</v>
+        <v>0.39515973</v>
       </c>
       <c r="M104" s="5" t="n">
-        <v>0.26386707</v>
+        <v>0.26537567</v>
       </c>
     </row>
     <row r="105">
@@ -5687,31 +5687,31 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>0.47656254</v>
+        <v>0.47432044</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>0.57322256</v>
+        <v>0.5625405999999999</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.32545465</v>
+        <v>0.32061537</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>0.5238905</v>
+        <v>0.52603828</v>
       </c>
       <c r="I105" s="5" t="n">
-        <v>0.57974319</v>
+        <v>0.57595852</v>
       </c>
       <c r="J105" s="5" t="n">
-        <v>0.6139569499999999</v>
+        <v>0.62007798</v>
       </c>
       <c r="K105" s="5" t="n">
-        <v>0.46902996</v>
+        <v>0.46836407</v>
       </c>
       <c r="L105" s="5" t="n">
-        <v>0.40575996</v>
+        <v>0.4066681</v>
       </c>
       <c r="M105" s="5" t="n">
-        <v>0.32144255</v>
+        <v>0.31430059</v>
       </c>
     </row>
     <row r="106">
@@ -5732,35 +5732,35 @@
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Lower-middle</t>
+          <t>Upper-middle</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0.46245548</v>
+        <v>0.45801214</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.48989495</v>
+        <v>0.48191721</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.4256638</v>
+        <v>0.41929185</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>0.46409244</v>
+        <v>0.46054862</v>
       </c>
       <c r="I106" s="5" t="n">
-        <v>0.41564389</v>
+        <v>0.41305694</v>
       </c>
       <c r="J106" s="5" t="n">
-        <v>0.68383634</v>
+        <v>0.67375554</v>
       </c>
       <c r="K106" s="5" t="n">
-        <v>0.46395648</v>
+        <v>0.46149</v>
       </c>
       <c r="L106" s="5" t="n">
-        <v>0.44161468</v>
+        <v>0.43817178</v>
       </c>
       <c r="M106" s="5" t="n">
-        <v>0.31494128</v>
+        <v>0.3158652</v>
       </c>
     </row>
     <row r="107">
@@ -5785,31 +5785,31 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>0.66222978</v>
+        <v>0.66588482</v>
       </c>
       <c r="F107" s="5" t="n">
-        <v>0.62021741</v>
+        <v>0.61850087</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.71065628</v>
+        <v>0.71603725</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>0.66202331</v>
+        <v>0.6734281600000001</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>0.64288015</v>
+        <v>0.64344912</v>
       </c>
       <c r="J107" s="5" t="n">
-        <v>0.84571757</v>
+        <v>0.84486703</v>
       </c>
       <c r="K107" s="5" t="n">
-        <v>0.63759478</v>
+        <v>0.64976545</v>
       </c>
       <c r="L107" s="5" t="n">
-        <v>0.60319451</v>
+        <v>0.61110321</v>
       </c>
       <c r="M107" s="5" t="n">
-        <v>0.5755542</v>
+        <v>0.56992743</v>
       </c>
     </row>
     <row r="108">
@@ -5834,31 +5834,31 @@
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>0.673841</v>
+        <v>0.67615026</v>
       </c>
       <c r="F108" s="5" t="n">
-        <v>0.74619062</v>
+        <v>0.74423835</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.7134623</v>
+        <v>0.71627159</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>0.61416576</v>
+        <v>0.62367211</v>
       </c>
       <c r="I108" s="5" t="n">
-        <v>0.74299301</v>
+        <v>0.73691071</v>
       </c>
       <c r="J108" s="5" t="n">
-        <v>0.77966166</v>
+        <v>0.77686582</v>
       </c>
       <c r="K108" s="5" t="n">
-        <v>0.59647569</v>
+        <v>0.60459405</v>
       </c>
       <c r="L108" s="5" t="n">
-        <v>0.62697251</v>
+        <v>0.6354059399999999</v>
       </c>
       <c r="M108" s="5" t="n">
-        <v>0.57080646</v>
+        <v>0.57124348</v>
       </c>
     </row>
     <row r="109">
@@ -5883,31 +5883,31 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0.61698631</v>
+        <v>0.62038201</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>0.59234578</v>
+        <v>0.60012779</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.67514043</v>
+        <v>0.68699595</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>0.41922259</v>
+        <v>0.41885684</v>
       </c>
       <c r="I109" s="5" t="n">
-        <v>0.42643125</v>
+        <v>0.43104005</v>
       </c>
       <c r="J109" s="5" t="n">
-        <v>0.9252145899999999</v>
+        <v>0.90854792</v>
       </c>
       <c r="K109" s="5" t="n">
-        <v>0.69952869</v>
+        <v>0.71108322</v>
       </c>
       <c r="L109" s="5" t="n">
-        <v>0.61473893</v>
+        <v>0.6240641099999999</v>
       </c>
       <c r="M109" s="5" t="n">
-        <v>0.5832682</v>
+        <v>0.58234018</v>
       </c>
     </row>
     <row r="110">
@@ -5932,31 +5932,31 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0.61299215</v>
+        <v>0.60654634</v>
       </c>
       <c r="F110" s="5" t="n">
-        <v>0.57550156</v>
+        <v>0.57461998</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.52700056</v>
+        <v>0.5145788</v>
       </c>
       <c r="H110" s="5" t="n">
-        <v>0.61837948</v>
+        <v>0.61488261</v>
       </c>
       <c r="I110" s="5" t="n">
-        <v>0.66345666</v>
+        <v>0.66113805</v>
       </c>
       <c r="J110" s="5" t="n">
-        <v>0.83042973</v>
+        <v>0.82942023</v>
       </c>
       <c r="K110" s="5" t="n">
-        <v>0.56250874</v>
+        <v>0.5558499</v>
       </c>
       <c r="L110" s="5" t="n">
-        <v>0.60646957</v>
+        <v>0.58870599</v>
       </c>
       <c r="M110" s="5" t="n">
-        <v>0.5201909300000001</v>
+        <v>0.51317514</v>
       </c>
     </row>
     <row r="111">
@@ -5981,31 +5981,31 @@
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0.40731793</v>
+        <v>0.40051811</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>0.30811294</v>
+        <v>0.29451274</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.40817835</v>
+        <v>0.4061885</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>0.4432149</v>
+        <v>0.43171484</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>0.34851382</v>
+        <v>0.33192962</v>
       </c>
       <c r="J111" s="5" t="n">
-        <v>0.51733056</v>
+        <v>0.5185698</v>
       </c>
       <c r="K111" s="5" t="n">
-        <v>0.4540307</v>
+        <v>0.44991817</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>0.49300879</v>
+        <v>0.49091007</v>
       </c>
       <c r="M111" s="5" t="n">
-        <v>0.28615342</v>
+        <v>0.28040116</v>
       </c>
     </row>
     <row r="112">
@@ -6030,31 +6030,31 @@
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>0.6338727</v>
+        <v>0.63570774</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.60539607</v>
+        <v>0.61076841</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.6919282</v>
+        <v>0.69213319</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>0.5564468299999999</v>
+        <v>0.5599388199999999</v>
       </c>
       <c r="I112" s="5" t="n">
-        <v>0.53018381</v>
+        <v>0.53546485</v>
       </c>
       <c r="J112" s="5" t="n">
-        <v>0.84869808</v>
+        <v>0.84865557</v>
       </c>
       <c r="K112" s="5" t="n">
-        <v>0.62584272</v>
+        <v>0.62495132</v>
       </c>
       <c r="L112" s="5" t="n">
-        <v>0.64786414</v>
+        <v>0.64057896</v>
       </c>
       <c r="M112" s="5" t="n">
-        <v>0.56462175</v>
+        <v>0.57317081</v>
       </c>
     </row>
     <row r="113">
@@ -6079,31 +6079,31 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>0.56109951</v>
+        <v>0.56188733</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>0.57113479</v>
+        <v>0.56772024</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.55938226</v>
+        <v>0.56125436</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>0.44711636</v>
+        <v>0.45413919</v>
       </c>
       <c r="I113" s="5" t="n">
-        <v>0.60094599</v>
+        <v>0.60039581</v>
       </c>
       <c r="J113" s="5" t="n">
-        <v>0.70600412</v>
+        <v>0.70679821</v>
       </c>
       <c r="K113" s="5" t="n">
-        <v>0.57233751</v>
+        <v>0.57358642</v>
       </c>
       <c r="L113" s="5" t="n">
-        <v>0.55705818</v>
+        <v>0.55167183</v>
       </c>
       <c r="M113" s="5" t="n">
-        <v>0.47481683</v>
+        <v>0.47953261</v>
       </c>
     </row>
     <row r="114">
@@ -6128,31 +6128,31 @@
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0.46606863</v>
+        <v>0.46194628</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.32328524</v>
+        <v>0.3152684</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.39014792</v>
+        <v>0.38378996</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>0.43783664</v>
+        <v>0.43203319</v>
       </c>
       <c r="I114" s="5" t="n">
-        <v>0.54608891</v>
+        <v>0.53534789</v>
       </c>
       <c r="J114" s="5" t="n">
-        <v>0.75953881</v>
+        <v>0.76040755</v>
       </c>
       <c r="K114" s="5" t="n">
-        <v>0.43417813</v>
+        <v>0.43926307</v>
       </c>
       <c r="L114" s="5" t="n">
-        <v>0.463174</v>
+        <v>0.45912142</v>
       </c>
       <c r="M114" s="5" t="n">
-        <v>0.37429939</v>
+        <v>0.37033873</v>
       </c>
     </row>
     <row r="115">
@@ -6177,31 +6177,31 @@
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>0.43981985</v>
+        <v>0.44013057</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>0.47420242</v>
+        <v>0.47107697</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.35902151</v>
+        <v>0.35903963</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>0.38314642</v>
+        <v>0.38175795</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>0.49131637</v>
+        <v>0.48751609</v>
       </c>
       <c r="J115" s="5" t="n">
-        <v>0.6645221</v>
+        <v>0.65990605</v>
       </c>
       <c r="K115" s="5" t="n">
-        <v>0.36037453</v>
+        <v>0.3653629</v>
       </c>
       <c r="L115" s="5" t="n">
-        <v>0.41120853</v>
+        <v>0.41476859</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>0.3747669</v>
+        <v>0.38161642</v>
       </c>
     </row>
     <row r="116">
@@ -6226,31 +6226,31 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0.7833441</v>
+        <v>0.78706845</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.67839401</v>
+        <v>0.68538539</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.93172939</v>
+        <v>0.93612259</v>
       </c>
       <c r="H116" s="5" t="n">
-        <v>0.61191259</v>
+        <v>0.61583107</v>
       </c>
       <c r="I116" s="5" t="n">
-        <v>0.67449486</v>
+        <v>0.68070895</v>
       </c>
       <c r="J116" s="5" t="n">
-        <v>0.93949003</v>
+        <v>0.94095196</v>
       </c>
       <c r="K116" s="5" t="n">
-        <v>0.86371623</v>
+        <v>0.86591462</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>0.80743235</v>
+        <v>0.8076399</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>0.75958335</v>
+        <v>0.7639931</v>
       </c>
     </row>
     <row r="117">
@@ -6275,31 +6275,31 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>0.64349895</v>
+        <v>0.63705605</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>0.6213058</v>
+        <v>0.60164021</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.51962793</v>
+        <v>0.51578781</v>
       </c>
       <c r="H117" s="5" t="n">
-        <v>0.68158158</v>
+        <v>0.6767436100000001</v>
       </c>
       <c r="I117" s="5" t="n">
-        <v>0.6981807</v>
+        <v>0.68068426</v>
       </c>
       <c r="J117" s="5" t="n">
-        <v>0.89788093</v>
+        <v>0.89343399</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>0.60852697</v>
+        <v>0.61283065</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>0.5424011</v>
+        <v>0.53889817</v>
       </c>
       <c r="M117" s="5" t="n">
-        <v>0.57848654</v>
+        <v>0.57642969</v>
       </c>
     </row>
     <row r="118">
@@ -6324,31 +6324,31 @@
         </is>
       </c>
       <c r="E118" s="5" t="n">
-        <v>0.6834045</v>
+        <v>0.68435966</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>0.6439637</v>
+        <v>0.64482887</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.64023001</v>
+        <v>0.63901823</v>
       </c>
       <c r="H118" s="5" t="n">
-        <v>0.6584922600000001</v>
+        <v>0.66305649</v>
       </c>
       <c r="I118" s="5" t="n">
-        <v>0.76149303</v>
+        <v>0.75935966</v>
       </c>
       <c r="J118" s="5" t="n">
-        <v>0.8867769</v>
+        <v>0.88780383</v>
       </c>
       <c r="K118" s="5" t="n">
-        <v>0.64934239</v>
+        <v>0.6537281700000001</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>0.66224915</v>
+        <v>0.65887837</v>
       </c>
       <c r="M118" s="5" t="n">
-        <v>0.56468856</v>
+        <v>0.56820363</v>
       </c>
     </row>
     <row r="119">
@@ -6373,31 +6373,31 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0.55944854</v>
+        <v>0.55606779</v>
       </c>
       <c r="F119" s="5" t="n">
-        <v>0.60876732</v>
+        <v>0.60473576</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.4583548</v>
+        <v>0.45148279</v>
       </c>
       <c r="H119" s="5" t="n">
-        <v>0.60606987</v>
+        <v>0.60755697</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>0.63035603</v>
+        <v>0.61623096</v>
       </c>
       <c r="J119" s="5" t="n">
-        <v>0.60241502</v>
+        <v>0.60233276</v>
       </c>
       <c r="K119" s="5" t="n">
-        <v>0.50532491</v>
+        <v>0.5176020099999999</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>0.5705316499999999</v>
+        <v>0.5602624</v>
       </c>
       <c r="M119" s="5" t="n">
-        <v>0.49376876</v>
+        <v>0.48833871</v>
       </c>
     </row>
     <row r="120">
@@ -6422,31 +6422,31 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0.71060828</v>
+        <v>0.70793273</v>
       </c>
       <c r="F120" s="5" t="n">
-        <v>0.68691895</v>
+        <v>0.68494795</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.72578626</v>
+        <v>0.72025695</v>
       </c>
       <c r="H120" s="5" t="n">
-        <v>0.6888713400000001</v>
+        <v>0.6915265</v>
       </c>
       <c r="I120" s="5" t="n">
-        <v>0.77623503</v>
+        <v>0.77856517</v>
       </c>
       <c r="J120" s="5" t="n">
-        <v>0.81611654</v>
+        <v>0.81482777</v>
       </c>
       <c r="K120" s="5" t="n">
-        <v>0.67639448</v>
+        <v>0.6643128</v>
       </c>
       <c r="L120" s="5" t="n">
-        <v>0.64555436</v>
+        <v>0.64280523</v>
       </c>
       <c r="M120" s="5" t="n">
-        <v>0.66898929</v>
+        <v>0.66621949</v>
       </c>
     </row>
     <row r="121">
@@ -6467,35 +6467,35 @@
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>Lower-middle</t>
+          <t>Upper-middle</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0.51212724</v>
+        <v>0.51220149</v>
       </c>
       <c r="F121" s="5" t="n">
-        <v>0.53526521</v>
+        <v>0.53225713</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.49167624</v>
+        <v>0.49258352</v>
       </c>
       <c r="H121" s="5" t="n">
-        <v>0.53272298</v>
+        <v>0.53483295</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>0.49757476</v>
+        <v>0.49224579</v>
       </c>
       <c r="J121" s="5" t="n">
-        <v>0.68491391</v>
+        <v>0.68437862</v>
       </c>
       <c r="K121" s="5" t="n">
-        <v>0.48694714</v>
+        <v>0.49710613</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>0.45504358</v>
+        <v>0.45461997</v>
       </c>
       <c r="M121" s="5" t="n">
-        <v>0.41287409</v>
+        <v>0.40958786</v>
       </c>
     </row>
     <row r="122">
@@ -6520,31 +6520,31 @@
         </is>
       </c>
       <c r="E122" s="5" t="n">
-        <v>0.63256454</v>
+        <v>0.63787329</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.6209116099999999</v>
+        <v>0.63325828</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.6365742599999999</v>
+        <v>0.63844391</v>
       </c>
       <c r="H122" s="5" t="n">
-        <v>0.46038717</v>
+        <v>0.46386135</v>
       </c>
       <c r="I122" s="5" t="n">
-        <v>0.69156274</v>
+        <v>0.69618791</v>
       </c>
       <c r="J122" s="5" t="n">
         <v>0.76166131</v>
       </c>
       <c r="K122" s="5" t="n">
-        <v>0.60751206</v>
+        <v>0.61130003</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>0.68720837</v>
+        <v>0.69256346</v>
       </c>
       <c r="M122" s="5" t="n">
-        <v>0.59469878</v>
+        <v>0.60571009</v>
       </c>
     </row>
     <row r="123">
@@ -6569,31 +6569,31 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0.61501577</v>
+        <v>0.61768251</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>0.60217467</v>
+        <v>0.60837606</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.62756236</v>
+        <v>0.63956013</v>
       </c>
       <c r="H123" s="5" t="n">
-        <v>0.49862487</v>
+        <v>0.49552049</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>0.66928535</v>
+        <v>0.6632059300000001</v>
       </c>
       <c r="J123" s="5" t="n">
-        <v>0.72999263</v>
+        <v>0.72999264</v>
       </c>
       <c r="K123" s="5" t="n">
-        <v>0.60137061</v>
+        <v>0.60211985</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>0.64269868</v>
+        <v>0.64862829</v>
       </c>
       <c r="M123" s="5" t="n">
-        <v>0.54841703</v>
+        <v>0.5540567</v>
       </c>
     </row>
     <row r="124">
@@ -6618,31 +6618,31 @@
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0.61505935</v>
+        <v>0.61986257</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0.57436862</v>
+        <v>0.59611898</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.6768417799999999</v>
+        <v>0.68095346</v>
       </c>
       <c r="H124" s="5" t="n">
-        <v>0.4836975</v>
+        <v>0.48013772</v>
       </c>
       <c r="I124" s="5" t="n">
-        <v>0.68531739</v>
+        <v>0.69080146</v>
       </c>
       <c r="J124" s="5" t="n">
         <v>0.7420896299999999</v>
       </c>
       <c r="K124" s="5" t="n">
-        <v>0.53630212</v>
+        <v>0.53451198</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>0.62691154</v>
+        <v>0.63538521</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>0.59494624</v>
+        <v>0.59890212</v>
       </c>
     </row>
     <row r="125">
@@ -6667,31 +6667,31 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>0.33694743</v>
+        <v>0.32755425</v>
       </c>
       <c r="F125" s="5" t="n">
-        <v>0.24959056</v>
+        <v>0.23504915</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.32055003</v>
+        <v>0.31006821</v>
       </c>
       <c r="H125" s="5" t="n">
-        <v>0.32698355</v>
+        <v>0.31295094</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>0.29676501</v>
+        <v>0.28634217</v>
       </c>
       <c r="J125" s="5" t="n">
-        <v>0.50003056</v>
+        <v>0.49662659</v>
       </c>
       <c r="K125" s="5" t="n">
-        <v>0.33151289</v>
+        <v>0.3222105</v>
       </c>
       <c r="L125" s="5" t="n">
-        <v>0.35091972</v>
+        <v>0.34331547</v>
       </c>
       <c r="M125" s="5" t="n">
-        <v>0.31922709</v>
+        <v>0.31387093</v>
       </c>
     </row>
     <row r="126">
@@ -6716,31 +6716,31 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0.49495845</v>
+        <v>0.49580148</v>
       </c>
       <c r="F126" s="5" t="n">
-        <v>0.49070522</v>
+        <v>0.49311699</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.43531318</v>
+        <v>0.4399928</v>
       </c>
       <c r="H126" s="5" t="n">
-        <v>0.38677815</v>
+        <v>0.38781167</v>
       </c>
       <c r="I126" s="5" t="n">
-        <v>0.52369454</v>
+        <v>0.5241721499999999</v>
       </c>
       <c r="J126" s="5" t="n">
-        <v>0.64626746</v>
+        <v>0.64617589</v>
       </c>
       <c r="K126" s="5" t="n">
-        <v>0.46398476</v>
+        <v>0.4687272</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>0.48813067</v>
+        <v>0.48233802</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>0.52479361</v>
+        <v>0.52407716</v>
       </c>
     </row>
     <row r="127">
@@ -6765,31 +6765,31 @@
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>0.85227449</v>
+        <v>0.85654111</v>
       </c>
       <c r="F127" s="5" t="n">
-        <v>0.84878175</v>
+        <v>0.8547976900000001</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.90787784</v>
+        <v>0.91757459</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>0.83124569</v>
+        <v>0.83904532</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>0.86998276</v>
+        <v>0.87702614</v>
       </c>
       <c r="J127" s="5" t="n">
-        <v>0.92502227</v>
+        <v>0.92248048</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>0.83176292</v>
+        <v>0.83642317</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>0.8261091</v>
+        <v>0.82667338</v>
       </c>
       <c r="M127" s="5" t="n">
-        <v>0.77741359</v>
+        <v>0.77830811</v>
       </c>
     </row>
     <row r="128">
@@ -6814,31 +6814,31 @@
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0.46076398</v>
+        <v>0.44439513</v>
       </c>
       <c r="F128" s="5" t="n">
-        <v>0.48708661</v>
+        <v>0.4641945</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.40212906</v>
+        <v>0.39501975</v>
       </c>
       <c r="H128" s="5" t="n">
-        <v>0.37177645</v>
+        <v>0.36878032</v>
       </c>
       <c r="I128" s="5" t="n">
-        <v>0.42656768</v>
+        <v>0.41607637</v>
       </c>
       <c r="J128" s="5" t="n">
-        <v>0.70365285</v>
+        <v>0.62440297</v>
       </c>
       <c r="K128" s="5" t="n">
-        <v>0.45880189</v>
+        <v>0.4632592</v>
       </c>
       <c r="L128" s="5" t="n">
-        <v>0.47174848</v>
+        <v>0.47170976</v>
       </c>
       <c r="M128" s="5" t="n">
-        <v>0.36434883</v>
+        <v>0.3517182</v>
       </c>
     </row>
     <row r="129">
@@ -6863,31 +6863,31 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0.5028867</v>
+        <v>0.49818691</v>
       </c>
       <c r="F129" s="5" t="n">
-        <v>0.47242739</v>
+        <v>0.46614671</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.45246622</v>
+        <v>0.44116897</v>
       </c>
       <c r="H129" s="5" t="n">
-        <v>0.4834591</v>
+        <v>0.48055619</v>
       </c>
       <c r="I129" s="5" t="n">
-        <v>0.49131535</v>
+        <v>0.48963647</v>
       </c>
       <c r="J129" s="5" t="n">
-        <v>0.74844152</v>
+        <v>0.74778202</v>
       </c>
       <c r="K129" s="5" t="n">
-        <v>0.44874613</v>
+        <v>0.44029704</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>0.50472238</v>
+        <v>0.49902684</v>
       </c>
       <c r="M129" s="5" t="n">
-        <v>0.42151548</v>
+        <v>0.420881</v>
       </c>
     </row>
     <row r="130">
@@ -6908,35 +6908,35 @@
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Lower-middle</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
-        <v>0.43259211</v>
+        <v>0.42393762</v>
       </c>
       <c r="F130" s="5" t="n">
-        <v>0.34066153</v>
+        <v>0.31957221</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.41954165</v>
+        <v>0.41392563</v>
       </c>
       <c r="H130" s="5" t="n">
-        <v>0.29661787</v>
+        <v>0.29186894</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>0.42435619</v>
+        <v>0.40647409</v>
       </c>
       <c r="J130" s="5" t="n">
-        <v>0.68531001</v>
+        <v>0.6795069500000001</v>
       </c>
       <c r="K130" s="5" t="n">
-        <v>0.49853171</v>
+        <v>0.49252989</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>0.45958244</v>
+        <v>0.45623698</v>
       </c>
       <c r="M130" s="5" t="n">
-        <v>0.33613547</v>
+        <v>0.33138624</v>
       </c>
     </row>
     <row r="131">
@@ -6961,31 +6961,31 @@
         </is>
       </c>
       <c r="E131" s="5" t="n">
-        <v>0.51133836</v>
+        <v>0.51759716</v>
       </c>
       <c r="F131" s="5" t="n">
-        <v>0.54108623</v>
+        <v>0.5557988699999999</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.48201461</v>
+        <v>0.49218268</v>
       </c>
       <c r="H131" s="5" t="n">
-        <v>0.52880704</v>
+        <v>0.53844253</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>0.5783005</v>
+        <v>0.58854912</v>
       </c>
       <c r="J131" s="5" t="n">
-        <v>0.64122753</v>
+        <v>0.64137499</v>
       </c>
       <c r="K131" s="5" t="n">
-        <v>0.48395599</v>
+        <v>0.48685693</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>0.53557323</v>
+        <v>0.5298135</v>
       </c>
       <c r="M131" s="5" t="n">
-        <v>0.29974177</v>
+        <v>0.30775869</v>
       </c>
     </row>
     <row r="132">
@@ -7010,31 +7010,31 @@
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0.48982978</v>
+        <v>0.48278786</v>
       </c>
       <c r="F132" s="5" t="n">
-        <v>0.48020311</v>
+        <v>0.46288316</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.47014168</v>
+        <v>0.46935637</v>
       </c>
       <c r="H132" s="5" t="n">
-        <v>0.44181165</v>
+        <v>0.43797282</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>0.45956314</v>
+        <v>0.44382368</v>
       </c>
       <c r="J132" s="5" t="n">
-        <v>0.71903494</v>
+        <v>0.7254200200000001</v>
       </c>
       <c r="K132" s="5" t="n">
-        <v>0.47591241</v>
+        <v>0.47148529</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>0.46918517</v>
+        <v>0.46294481</v>
       </c>
       <c r="M132" s="5" t="n">
-        <v>0.40278617</v>
+        <v>0.38841669</v>
       </c>
     </row>
     <row r="133">
@@ -7059,31 +7059,31 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>0.40770137</v>
+        <v>0.40590502</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>0.28126499</v>
+        <v>0.27699405</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.43531877</v>
+        <v>0.44027331</v>
       </c>
       <c r="H133" s="5" t="n">
-        <v>0.39174864</v>
+        <v>0.37954746</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>0.29815782</v>
+        <v>0.28541394</v>
       </c>
       <c r="J133" s="5" t="n">
-        <v>0.70856355</v>
+        <v>0.73593195</v>
       </c>
       <c r="K133" s="5" t="n">
-        <v>0.41173102</v>
+        <v>0.40775671</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>0.39630338</v>
+        <v>0.38952125</v>
       </c>
       <c r="M133" s="5" t="n">
-        <v>0.33852278</v>
+        <v>0.33180148</v>
       </c>
     </row>
     <row r="134">
@@ -7108,31 +7108,31 @@
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>0.38402636</v>
+        <v>0.37750656</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>0.37137813</v>
+        <v>0.36021578</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.26312422</v>
+        <v>0.26446332</v>
       </c>
       <c r="H134" s="5" t="n">
-        <v>0.38087226</v>
+        <v>0.3771458</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>0.33596579</v>
+        <v>0.32312652</v>
       </c>
       <c r="J134" s="5" t="n">
-        <v>0.5910506800000001</v>
+        <v>0.58740393</v>
       </c>
       <c r="K134" s="5" t="n">
-        <v>0.41237944</v>
+        <v>0.41188133</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>0.41296318</v>
+        <v>0.40205735</v>
       </c>
       <c r="M134" s="5" t="n">
-        <v>0.30447719</v>
+        <v>0.29375841</v>
       </c>
     </row>
     <row r="135">
@@ -7157,31 +7157,31 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>0.48365439</v>
+        <v>0.48633961</v>
       </c>
       <c r="F135" s="5" t="n">
-        <v>0.45910104</v>
+        <v>0.46121122</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.33431892</v>
+        <v>0.34344826</v>
       </c>
       <c r="H135" s="5" t="n">
-        <v>0.5572781</v>
+        <v>0.55838284</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>0.57376687</v>
+        <v>0.57713344</v>
       </c>
       <c r="J135" s="5" t="n">
-        <v>0.6218394900000001</v>
+        <v>0.62425046</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>0.42571617</v>
+        <v>0.42801145</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>0.53151895</v>
+        <v>0.52353096</v>
       </c>
       <c r="M135" s="5" t="n">
-        <v>0.36569554</v>
+        <v>0.37474825</v>
       </c>
     </row>
     <row r="136">
@@ -7206,31 +7206,31 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>0.63984888</v>
+        <v>0.64185401</v>
       </c>
       <c r="F136" s="5" t="n">
-        <v>0.58706526</v>
+        <v>0.59009363</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.77552036</v>
+        <v>0.77703407</v>
       </c>
       <c r="H136" s="5" t="n">
-        <v>0.34729005</v>
+        <v>0.35105737</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>0.44144472</v>
+        <v>0.43665823</v>
       </c>
       <c r="J136" s="5" t="n">
-        <v>0.91363888</v>
+        <v>0.91675953</v>
       </c>
       <c r="K136" s="5" t="n">
-        <v>0.70376451</v>
+        <v>0.71568177</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>0.67354222</v>
+        <v>0.67459414</v>
       </c>
       <c r="M136" s="5" t="n">
-        <v>0.67652504</v>
+        <v>0.67295337</v>
       </c>
     </row>
     <row r="137">
@@ -7255,31 +7255,31 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>0.78447329</v>
+        <v>0.77799816</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>0.82343992</v>
+        <v>0.8143662699999999</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.83217157</v>
+        <v>0.82846778</v>
       </c>
       <c r="H137" s="5" t="n">
-        <v>0.79800084</v>
+        <v>0.78847579</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>0.79656321</v>
+        <v>0.78720922</v>
       </c>
       <c r="J137" s="5" t="n">
-        <v>0.84229444</v>
+        <v>0.83958376</v>
       </c>
       <c r="K137" s="5" t="n">
-        <v>0.7831597300000001</v>
+        <v>0.78004971</v>
       </c>
       <c r="L137" s="5" t="n">
-        <v>0.70123178</v>
+        <v>0.6891501</v>
       </c>
       <c r="M137" s="5" t="n">
-        <v>0.69892479</v>
+        <v>0.69668266</v>
       </c>
     </row>
     <row r="138">
@@ -7304,31 +7304,31 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>0.67977332</v>
+        <v>0.66772205</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>0.63129882</v>
+        <v>0.62008538</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.7224283500000001</v>
+        <v>0.69960157</v>
       </c>
       <c r="H138" s="5" t="n">
-        <v>0.71709331</v>
+        <v>0.706575</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>0.64973369</v>
+        <v>0.63133361</v>
       </c>
       <c r="J138" s="5" t="n">
-        <v>0.83016125</v>
+        <v>0.84124034</v>
       </c>
       <c r="K138" s="5" t="n">
-        <v>0.6970951</v>
+        <v>0.68134068</v>
       </c>
       <c r="L138" s="5" t="n">
-        <v>0.61520873</v>
+        <v>0.59712104</v>
       </c>
       <c r="M138" s="5" t="n">
-        <v>0.57516731</v>
+        <v>0.56447878</v>
       </c>
     </row>
     <row r="139">
@@ -7353,31 +7353,31 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0.71827858</v>
+        <v>0.7224582899999999</v>
       </c>
       <c r="F139" s="5" t="n">
-        <v>0.76042576</v>
+        <v>0.76256148</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.7369417700000001</v>
+        <v>0.74151068</v>
       </c>
       <c r="H139" s="5" t="n">
-        <v>0.73179752</v>
+        <v>0.74341222</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>0.78906973</v>
+        <v>0.79230997</v>
       </c>
       <c r="J139" s="5" t="n">
-        <v>0.70446824</v>
+        <v>0.70997587</v>
       </c>
       <c r="K139" s="5" t="n">
-        <v>0.72388845</v>
+        <v>0.72908427</v>
       </c>
       <c r="L139" s="5" t="n">
-        <v>0.7139136699999999</v>
+        <v>0.71792827</v>
       </c>
       <c r="M139" s="5" t="n">
-        <v>0.58572347</v>
+        <v>0.58288354</v>
       </c>
     </row>
     <row r="140">
@@ -7402,31 +7402,31 @@
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>0.49687625</v>
+        <v>0.49841584</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>0.37313648</v>
+        <v>0.37203999</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.47305617</v>
+        <v>0.48229806</v>
       </c>
       <c r="H140" s="5" t="n">
-        <v>0.3672664</v>
+        <v>0.36487522</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>0.43414079</v>
+        <v>0.43394964</v>
       </c>
       <c r="J140" s="5" t="n">
-        <v>0.89854587</v>
+        <v>0.90368069</v>
       </c>
       <c r="K140" s="5" t="n">
-        <v>0.45127891</v>
+        <v>0.45893707</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>0.51975153</v>
+        <v>0.51645073</v>
       </c>
       <c r="M140" s="5" t="n">
-        <v>0.45783387</v>
+        <v>0.45509529</v>
       </c>
     </row>
     <row r="141">
@@ -7447,35 +7447,35 @@
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>Upper-middle</t>
+          <t>Lower-middle</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>0.25974105</v>
+        <v>0.25921234</v>
       </c>
       <c r="F141" s="5" t="n">
-        <v>0.1780454</v>
+        <v>0.1751266</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.26295179</v>
+        <v>0.25839707</v>
       </c>
       <c r="H141" s="5" t="n">
-        <v>0.2664677</v>
+        <v>0.26160302</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>0.2767358</v>
+        <v>0.27366864</v>
       </c>
       <c r="J141" s="5" t="n">
-        <v>0.53023665</v>
+        <v>0.53532314</v>
       </c>
       <c r="K141" s="5" t="n">
-        <v>0.20111778</v>
+        <v>0.20130961</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>0.2553775</v>
+        <v>0.25808447</v>
       </c>
       <c r="M141" s="5" t="n">
-        <v>0.10699577</v>
+        <v>0.11018614</v>
       </c>
     </row>
     <row r="142">
@@ -7496,35 +7496,35 @@
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>Lower-middle</t>
+          <t>Upper-middle</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>0.49549633</v>
+        <v>0.49722613</v>
       </c>
       <c r="F142" s="5" t="n">
-        <v>0.4544079</v>
+        <v>0.46679774</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.42566171</v>
+        <v>0.4295123</v>
       </c>
       <c r="H142" s="5" t="n">
-        <v>0.4278717</v>
+        <v>0.42912628</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>0.46802869</v>
+        <v>0.46323748</v>
       </c>
       <c r="J142" s="5" t="n">
-        <v>0.78445061</v>
+        <v>0.78471424</v>
       </c>
       <c r="K142" s="5" t="n">
-        <v>0.45383514</v>
+        <v>0.45431473</v>
       </c>
       <c r="L142" s="5" t="n">
-        <v>0.46932404</v>
+        <v>0.46891427</v>
       </c>
       <c r="M142" s="5" t="n">
-        <v>0.48039085</v>
+        <v>0.48119203</v>
       </c>
     </row>
     <row r="143">
@@ -7549,31 +7549,31 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>0.44991896</v>
+        <v>0.44117597</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>0.46297393</v>
+        <v>0.44563729</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.36229106</v>
+        <v>0.36185748</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>0.40628685</v>
+        <v>0.38776615</v>
       </c>
       <c r="I143" s="5" t="n">
-        <v>0.39512437</v>
+        <v>0.38200322</v>
       </c>
       <c r="J143" s="5" t="n">
-        <v>0.67584925</v>
+        <v>0.6777289399999999</v>
       </c>
       <c r="K143" s="5" t="n">
-        <v>0.42067346</v>
+        <v>0.40974776</v>
       </c>
       <c r="L143" s="5" t="n">
-        <v>0.46934906</v>
+        <v>0.46162049</v>
       </c>
       <c r="M143" s="5" t="n">
-        <v>0.4068037</v>
+        <v>0.40304642</v>
       </c>
     </row>
     <row r="144">
@@ -7598,31 +7598,31 @@
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>0.39277198</v>
+        <v>0.39559456</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>0.31818033</v>
+        <v>0.32017002</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.30990986</v>
+        <v>0.3176292</v>
       </c>
       <c r="H144" s="5" t="n">
-        <v>0.32235166</v>
+        <v>0.33499912</v>
       </c>
       <c r="I144" s="5" t="n">
-        <v>0.33342482</v>
+        <v>0.3299166</v>
       </c>
       <c r="J144" s="5" t="n">
-        <v>0.68388035</v>
+        <v>0.68259088</v>
       </c>
       <c r="K144" s="5" t="n">
-        <v>0.36163718</v>
+        <v>0.3629911</v>
       </c>
       <c r="L144" s="5" t="n">
-        <v>0.46172831</v>
+        <v>0.46590131</v>
       </c>
       <c r="M144" s="5" t="n">
-        <v>0.35106332</v>
+        <v>0.35055825</v>
       </c>
     </row>
   </sheetData>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T01:10:47+00:00</t>
+          <t>2026-10-21T08:10:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T08:10:35+00:00</t>
+          <t>2026-10-21T15:47:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T15:47:26+00:00</t>
+          <t>2026-10-21T22:04:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T22:04:30+00:00</t>
+          <t>2026-10-22T01:07:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T01:07:34+00:00</t>
+          <t>2026-10-22T08:10:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T08:10:44+00:00</t>
+          <t>2026-10-22T15:46:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T15:46:33+00:00</t>
+          <t>2026-10-22T22:01:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T22:01:48+00:00</t>
+          <t>2026-10-23T01:08:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T01:08:30+00:00</t>
+          <t>2026-10-23T08:09:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T08:09:26+00:00</t>
+          <t>2026-10-23T15:34:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T15:34:39+00:00</t>
+          <t>2026-10-23T21:49:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T21:49:27+00:00</t>
+          <t>2026-10-24T01:17:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T01:17:33+00:00</t>
+          <t>2026-10-24T07:47:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T07:47:57+00:00</t>
+          <t>2026-10-24T09:10:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T09:10:22+00:00</t>
+          <t>2026-10-24T14:12:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T14:12:54+00:00</t>
+          <t>2026-10-24T15:23:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T15:23:33+00:00</t>
+          <t>2026-10-24T17:44:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T17:44:57+00:00</t>
+          <t>2026-10-24T21:21:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T21:21:34+00:00</t>
+          <t>2026-10-25T00:43:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T00:43:22+00:00</t>
+          <t>2026-10-25T07:58:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T07:58:11+00:00</t>
+          <t>2026-10-25T14:43:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T14:43:26+00:00</t>
+          <t>2026-10-25T18:01:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T18:01:17+00:00</t>
+          <t>2026-10-25T21:26:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T21:26:21+00:00</t>
+          <t>2026-10-26T00:57:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T00:57:41+00:00</t>
+          <t>2026-10-26T08:29:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T08:29:34+00:00</t>
+          <t>2026-10-26T17:05:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T17:05:45+00:00</t>
+          <t>2026-10-26T22:58:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T22:58:36+00:00</t>
+          <t>2026-10-27T01:45:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:45:25+00:00</t>
+          <t>2026-10-27T01:48:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:48:29+00:00</t>
+          <t>2026-10-27T08:32:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T08:32:28+00:00</t>
+          <t>2026-10-27T16:08:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T16:08:43+00:00</t>
+          <t>2026-10-27T22:47:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T22:47:31+00:00</t>
+          <t>2026-10-28T01:56:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T01:56:52+00:00</t>
+          <t>2026-10-28T09:11:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T09:11:58+00:00</t>
+          <t>2026-10-28T16:56:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T16:56:26+00:00</t>
+          <t>2026-10-28T22:56:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:56:14+00:00</t>
+          <t>2026-10-29T02:01:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T02:01:40+00:00</t>
+          <t>2026-10-29T06:41:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T06:41:51+00:00</t>
+          <t>2026-10-29T09:09:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T09:09:56+00:00</t>
+          <t>2026-10-29T17:13:57+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T17:13:57+00:00</t>
+          <t>2026-10-29T23:04:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T23:04:21+00:00</t>
+          <t>2026-10-30T02:17:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T02:17:34+00:00</t>
+          <t>2026-10-30T09:20:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T09:20:54+00:00</t>
+          <t>2026-10-30T16:55:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T16:55:10+00:00</t>
+          <t>2026-10-30T22:45:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/wjp-rule-of-law.xlsx
+++ b/public/downloads/wjp-rule-of-law.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T22:45:29+00:00</t>
+          <t>2026-10-31T01:56:46+00:00</t>
         </is>
       </c>
     </row>
